--- a/output/IIJP_resultados.xlsx
+++ b/output/IIJP_resultados.xlsx
@@ -464,7 +464,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ultimo IPC: 2026-08 | ultimo haber: 2026-09 | ultima IMIG: 2026-08</t>
+          <t>Ultimo IPC: 2026-08 | ultimo haber: 2026-09 | ultima IMIG: 2026-08 | replicas bootstrap: 500</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Montos fiscales en millones de pesos corrientes. Ver README y docs/ para la metodologia.</t>
+          <t>Montos fiscales en millones de pesos corrientes. Metodologia: README y docs/ del repo github.com/santiagoriverti/IPC_jubilados.</t>
         </is>
       </c>
     </row>
@@ -9212,10 +9212,10 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>119244.264</v>
+        <v>119254.8353</v>
       </c>
       <c r="I87" t="n">
-        <v>119561.403</v>
+        <v>119550.8317</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
@@ -9256,10 +9256,10 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>149651.55132</v>
+        <v>149629.04185091</v>
       </c>
       <c r="I88" t="n">
-        <v>151006.051989</v>
+        <v>151004.65552027</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
@@ -9300,10 +9300,10 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>180479.77089192</v>
+        <v>180467.5873763825</v>
       </c>
       <c r="I89" t="n">
-        <v>183321.347114646</v>
+        <v>183334.7522671598</v>
       </c>
       <c r="J89" t="n">
         <v>70000</v>
@@ -9352,13 +9352,13 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>204303.1006496535</v>
+        <v>204361.4959450155</v>
       </c>
       <c r="I90" t="n">
-        <v>208619.6930164671</v>
+        <v>208653.2815552546</v>
       </c>
       <c r="J90" t="n">
-        <v>79240.00000000001</v>
+        <v>79268</v>
       </c>
       <c r="K90" t="n">
         <v>82731.69424653072</v>
@@ -9395,22 +9395,22 @@
         <v>260141.6</v>
       </c>
       <c r="E91" t="n">
-        <v>190124.4741</v>
+        <v>190141.602431</v>
       </c>
       <c r="F91" t="n">
-        <v>189953.19079</v>
+        <v>189987.447452</v>
       </c>
       <c r="G91" t="n">
-        <v>0.999099099099099</v>
+        <v>0.999189262228628</v>
       </c>
       <c r="H91" t="n">
-        <v>226776.4417211154</v>
+        <v>226861.6966485618</v>
       </c>
       <c r="I91" t="n">
-        <v>231359.239555262</v>
+        <v>231438.2199010884</v>
       </c>
       <c r="J91" t="n">
-        <v>87956.40000000002</v>
+        <v>87995.40680000001</v>
       </c>
       <c r="K91" t="n">
         <v>88158.6492245984</v>
@@ -9447,22 +9447,22 @@
         <v>276931.1</v>
       </c>
       <c r="E92" t="n">
-        <v>206855.4278208</v>
+        <v>206931.1059256573</v>
       </c>
       <c r="F92" t="n">
-        <v>207618.83753347</v>
+        <v>207694.2775545264</v>
       </c>
       <c r="G92" t="n">
-        <v>1.003690547164812</v>
+        <v>1.00368804692487</v>
       </c>
       <c r="H92" t="n">
-        <v>246732.7685925736</v>
+        <v>246893.5844626298</v>
       </c>
       <c r="I92" t="n">
-        <v>252875.6488339014</v>
+        <v>253008.2619958698</v>
       </c>
       <c r="J92" t="n">
-        <v>95696.56320000003</v>
+        <v>95765.40122044002</v>
       </c>
       <c r="K92" t="n">
         <v>91743.87907408943</v>
@@ -9499,22 +9499,22 @@
         <v>285580.82</v>
       </c>
       <c r="E93" t="n">
-        <v>215543.3557892737</v>
+        <v>215580.8261533498</v>
       </c>
       <c r="F93" t="n">
-        <v>215923.5910348088</v>
+        <v>215918.9709456856</v>
       </c>
       <c r="G93" t="n">
-        <v>1.001764077784457</v>
+        <v>1.00156852906805</v>
       </c>
       <c r="H93" t="n">
-        <v>257095.5448734617</v>
+        <v>257213.7362931677</v>
       </c>
       <c r="I93" t="n">
-        <v>262990.6747872574</v>
+        <v>263027.3891709062</v>
       </c>
       <c r="J93" t="n">
-        <v>99715.81885440004</v>
+        <v>99768.39499145442</v>
       </c>
       <c r="K93" t="n">
         <v>91875.34506393042</v>
@@ -9551,22 +9551,22 @@
         <v>295454.42</v>
       </c>
       <c r="E94" t="n">
-        <v>225458.3501555803</v>
+        <v>225454.4279911732</v>
       </c>
       <c r="F94" t="n">
-        <v>226071.9998134448</v>
+        <v>226110.346374322</v>
       </c>
       <c r="G94" t="n">
-        <v>1.002721787227845</v>
+        <v>1.002909316924902</v>
       </c>
       <c r="H94" t="n">
-        <v>268921.9399376409</v>
+        <v>268994.1254153948</v>
       </c>
       <c r="I94" t="n">
-        <v>275351.2365022585</v>
+        <v>275442.2819397729</v>
       </c>
       <c r="J94" t="n">
-        <v>104302.7465217024</v>
+        <v>104337.787482063</v>
       </c>
       <c r="K94" t="n">
         <v>92234.94546660256</v>
@@ -9603,22 +9603,22 @@
         <v>304540.23</v>
       </c>
       <c r="E95" t="n">
-        <v>234476.6841618035</v>
+        <v>234540.2414392175</v>
       </c>
       <c r="F95" t="n">
-        <v>235340.951805796</v>
+        <v>235380.8705756692</v>
       </c>
       <c r="G95" t="n">
-        <v>1.003685942792487</v>
+        <v>1.003584157376548</v>
       </c>
       <c r="H95" t="n">
-        <v>279678.8175351465</v>
+        <v>279834.5886696352</v>
       </c>
       <c r="I95" t="n">
-        <v>286640.6371988511</v>
+        <v>286735.4154993036</v>
       </c>
       <c r="J95" t="n">
-        <v>108474.8563825705</v>
+        <v>108542.6003175902</v>
       </c>
       <c r="K95" t="n">
         <v>92734.84624735358</v>
@@ -9655,22 +9655,22 @@
         <v>314320.56</v>
       </c>
       <c r="E96" t="n">
-        <v>244324.7048965992</v>
+        <v>244320.5695072329</v>
       </c>
       <c r="F96" t="n">
-        <v>245225.2717816394</v>
+        <v>245337.48140102</v>
       </c>
       <c r="G96" t="n">
-        <v>1.003685942792487</v>
+        <v>1.004162203353725</v>
       </c>
       <c r="H96" t="n">
-        <v>291425.3278716227</v>
+        <v>291503.691017159</v>
       </c>
       <c r="I96" t="n">
-        <v>298679.5439612028</v>
+        <v>298864.3235749241</v>
       </c>
       <c r="J96" t="n">
-        <v>113030.8003506385</v>
+        <v>113068.8267508337</v>
       </c>
       <c r="K96" t="n">
         <v>94069.77953254395</v>
@@ -9707,22 +9707,22 @@
         <v>322798.48</v>
       </c>
       <c r="E97" t="n">
-        <v>252876.0695679802</v>
+        <v>252798.4932691339</v>
       </c>
       <c r="F97" t="n">
-        <v>253562.9310222152</v>
+        <v>253777.090761215</v>
       </c>
       <c r="G97" t="n">
-        <v>1.002716197920224</v>
+        <v>1.003871057455391</v>
       </c>
       <c r="H97" t="n">
-        <v>301625.2143471295</v>
+        <v>301618.8690954545</v>
       </c>
       <c r="I97" t="n">
-        <v>308834.6484558837</v>
+        <v>309145.2563059015</v>
       </c>
       <c r="J97" t="n">
-        <v>116986.8783629109</v>
+        <v>116992.3150390876</v>
       </c>
       <c r="K97" t="n">
         <v>95028.0921528269</v>
@@ -9759,22 +9759,22 @@
         <v>329598.76</v>
       </c>
       <c r="E98" t="n">
-        <v>259703.7234463156</v>
+        <v>259598.7727380735</v>
       </c>
       <c r="F98" t="n">
-        <v>260155.5672287928</v>
+        <v>260476.8059573111</v>
       </c>
       <c r="G98" t="n">
-        <v>1.001739843297128</v>
+        <v>1.003382270301114</v>
       </c>
       <c r="H98" t="n">
-        <v>309769.0951345019</v>
+        <v>309732.4166741222</v>
       </c>
       <c r="I98" t="n">
-        <v>316864.3493157367</v>
+        <v>317306.6910723773</v>
       </c>
       <c r="J98" t="n">
-        <v>120145.5240787094</v>
+        <v>120139.4083136391</v>
       </c>
       <c r="K98" t="n">
         <v>95015.03747717013</v>
@@ -9811,22 +9811,22 @@
         <v>335907.01</v>
       </c>
       <c r="E99" t="n">
-        <v>265936.6128090272</v>
+        <v>265907.0229156087</v>
       </c>
       <c r="F99" t="n">
-        <v>266399.3008422838</v>
+        <v>266702.2016196909</v>
       </c>
       <c r="G99" t="n">
-        <v>1.001739843297128</v>
+        <v>1.002990438896134</v>
       </c>
       <c r="H99" t="n">
-        <v>317203.55341773</v>
+        <v>317258.9143993033</v>
       </c>
       <c r="I99" t="n">
-        <v>324469.0936993144</v>
+        <v>324890.3209890071</v>
       </c>
       <c r="J99" t="n">
-        <v>123029.0166565985</v>
+        <v>123058.7959356605</v>
       </c>
       <c r="K99" t="n">
         <v>95218.57453527581</v>
@@ -9863,22 +9863,22 @@
         <v>343086.5</v>
       </c>
       <c r="E100" t="n">
-        <v>273116.9013548709</v>
+        <v>273086.5125343301</v>
       </c>
       <c r="F100" t="n">
-        <v>273592.0819650255</v>
+        <v>273929.8312835845</v>
       </c>
       <c r="G100" t="n">
-        <v>1.001739843297128</v>
+        <v>1.003088101061558</v>
       </c>
       <c r="H100" t="n">
-        <v>325768.0493600087</v>
+        <v>325824.9050880845</v>
       </c>
       <c r="I100" t="n">
-        <v>333229.7592291959</v>
+        <v>333694.8486878092</v>
       </c>
       <c r="J100" t="n">
-        <v>126350.8001063266</v>
+        <v>126381.3834259233</v>
       </c>
       <c r="K100" t="n">
         <v>95496.01775153728</v>
@@ -9915,22 +9915,22 @@
         <v>349121.71</v>
       </c>
       <c r="E101" t="n">
-        <v>279125.4731846781</v>
+        <v>279121.7244613388</v>
       </c>
       <c r="F101" t="n">
-        <v>279611.107768256</v>
+        <v>280038.4665212084</v>
       </c>
       <c r="G101" t="n">
-        <v>1.001739843297128</v>
+        <v>1.003284380897398</v>
       </c>
       <c r="H101" t="n">
-        <v>332934.9464459289</v>
+        <v>333025.6354905311</v>
       </c>
       <c r="I101" t="n">
-        <v>340560.8139322382</v>
+        <v>341136.2438135473</v>
       </c>
       <c r="J101" t="n">
-        <v>129130.5177086658</v>
+        <v>129174.4119996362</v>
       </c>
       <c r="K101" t="n">
         <v>94097.27622214259</v>
@@ -9967,22 +9967,22 @@
         <v>355820.63</v>
       </c>
       <c r="E102" t="n">
-        <v>285824.4845411104</v>
+        <v>285820.645848411</v>
       </c>
       <c r="F102" t="n">
-        <v>286601.3854624624</v>
+        <v>287095.4358775428</v>
       </c>
       <c r="G102" t="n">
-        <v>1.002718104862847</v>
+        <v>1.004460104781262</v>
       </c>
       <c r="H102" t="n">
-        <v>340925.3851606312</v>
+        <v>341018.2507423038</v>
       </c>
       <c r="I102" t="n">
-        <v>349074.8342805441</v>
+        <v>349732.8771576487</v>
       </c>
       <c r="J102" t="n">
-        <v>132229.6501336738</v>
+        <v>132274.5978876275</v>
       </c>
       <c r="K102" t="n">
         <v>93748.6153997815</v>
@@ -10019,22 +10019,22 @@
         <v>366481.74</v>
       </c>
       <c r="E103" t="n">
-        <v>296399.9904691314</v>
+        <v>296481.7559385567</v>
       </c>
       <c r="F103" t="n">
-        <v>296345.8325681862</v>
+        <v>296827.9711537915</v>
       </c>
       <c r="G103" t="n">
-        <v>0.9998172810300717</v>
+        <v>1.00116774542885</v>
       </c>
       <c r="H103" t="n">
-        <v>353539.6244115746</v>
+        <v>353738.2314949918</v>
       </c>
       <c r="I103" t="n">
-        <v>360943.3786460827</v>
+        <v>361588.821693293</v>
       </c>
       <c r="J103" t="n">
-        <v>137122.1471886197</v>
+        <v>137208.440388836</v>
       </c>
       <c r="K103" t="n">
         <v>95807.26774995995</v>
@@ -10071,22 +10071,22 @@
         <v>374723.93</v>
       </c>
       <c r="E104" t="n">
-        <v>304699.1902022671</v>
+        <v>304723.9487536486</v>
       </c>
       <c r="F104" t="n">
-        <v>304347.1700475272</v>
+        <v>304693.912389367</v>
       </c>
       <c r="G104" t="n">
-        <v>0.9988446961263459</v>
+        <v>0.999901430903595</v>
       </c>
       <c r="H104" t="n">
-        <v>363438.7338950987</v>
+        <v>363572.1543305526</v>
       </c>
       <c r="I104" t="n">
-        <v>370688.8498695269</v>
+        <v>371170.9254681653</v>
       </c>
       <c r="J104" t="n">
-        <v>140961.5673099011</v>
+        <v>141022.8350316456</v>
       </c>
       <c r="K104" t="n">
         <v>96901.9394185229</v>
@@ -10123,22 +10123,22 @@
         <v>379294.79</v>
       </c>
       <c r="E105" t="n">
-        <v>309269.6780553011</v>
+        <v>309294.8079849533</v>
       </c>
       <c r="F105" t="n">
-        <v>309216.7247682876</v>
+        <v>309416.6680314022</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9998287795708054</v>
+        <v>1.000393993184828</v>
       </c>
       <c r="H105" t="n">
-        <v>368890.3149035251</v>
+        <v>369025.7366455109</v>
       </c>
       <c r="I105" t="n">
-        <v>376619.8714674393</v>
+        <v>376924.0748129218</v>
       </c>
       <c r="J105" t="n">
-        <v>143075.9908195496</v>
+        <v>143138.1775571203</v>
       </c>
       <c r="K105" t="n">
         <v>96519.96436079894</v>
@@ -10175,22 +10175,22 @@
         <v>384305.37</v>
       </c>
       <c r="E106" t="n">
-        <v>314217.992904186</v>
+        <v>314305.3838743096</v>
       </c>
       <c r="F106" t="n">
-        <v>314473.4090893485</v>
+        <v>314522.0430539203</v>
       </c>
       <c r="G106" t="n">
-        <v>1.000812863015265</v>
+        <v>1.000689326975377</v>
       </c>
       <c r="H106" t="n">
-        <v>374792.5599419815</v>
+        <v>375003.9535791682</v>
       </c>
       <c r="I106" t="n">
-        <v>383022.4092823857</v>
+        <v>383143.322047335</v>
       </c>
       <c r="J106" t="n">
-        <v>145365.2066726624</v>
+        <v>145457.0160335457</v>
       </c>
       <c r="K106" t="n">
         <v>96277.61981183944</v>
@@ -10227,22 +10227,22 @@
         <v>390277.17</v>
       </c>
       <c r="E107" t="n">
-        <v>320188.1347693655</v>
+        <v>320277.1861679215</v>
       </c>
       <c r="F107" t="n">
-        <v>320762.8772711355</v>
+        <v>320686.6750977772</v>
       </c>
       <c r="G107" t="n">
-        <v>1.001795014990746</v>
+        <v>1.001278545421094</v>
       </c>
       <c r="H107" t="n">
-        <v>381913.6185808791</v>
+        <v>382129.0286971724</v>
       </c>
       <c r="I107" t="n">
-        <v>390682.8574680334</v>
+        <v>390652.9311594628</v>
       </c>
       <c r="J107" t="n">
-        <v>148127.1455994429</v>
+        <v>148220.699338183</v>
       </c>
       <c r="K107" t="n">
         <v>96111.654159395</v>
@@ -10279,22 +10279,22 @@
         <v>396298.38</v>
       </c>
       <c r="E108" t="n">
-        <v>326271.7093299834</v>
+        <v>326298.3972678783</v>
       </c>
       <c r="F108" t="n">
-        <v>326857.371939287</v>
+        <v>326651.4472545958</v>
       </c>
       <c r="G108" t="n">
-        <v>1.001795014990746</v>
+        <v>1.001081985047042</v>
       </c>
       <c r="H108" t="n">
-        <v>389169.9773339158</v>
+        <v>389313.0544366792</v>
       </c>
       <c r="I108" t="n">
-        <v>398105.831759926</v>
+        <v>397919.0756790288</v>
       </c>
       <c r="J108" t="n">
-        <v>150941.5613658323</v>
+        <v>151007.2484857408</v>
       </c>
       <c r="K108" t="n">
         <v>95677.8326172236</v>
@@ -10331,22 +10331,22 @@
         <v>403085.39</v>
       </c>
       <c r="E109" t="n">
-        <v>333123.415225913</v>
+        <v>333085.4039310502</v>
       </c>
       <c r="F109" t="n">
-        <v>334048.2341219513</v>
+        <v>333739.7836600206</v>
       </c>
       <c r="G109" t="n">
-        <v>1.002776205015223</v>
+        <v>1.001964600433545</v>
       </c>
       <c r="H109" t="n">
-        <v>397342.546857928</v>
+        <v>397410.765968962</v>
       </c>
       <c r="I109" t="n">
-        <v>406864.1600586444</v>
+        <v>406553.9196212637</v>
       </c>
       <c r="J109" t="n">
-        <v>154111.3341545148</v>
+        <v>154148.1992542442</v>
       </c>
       <c r="K109" t="n">
         <v>95310.96892028471</v>
@@ -10383,22 +10383,22 @@
         <v>410879.59</v>
       </c>
       <c r="E110" t="n">
-        <v>340785.253776109</v>
+        <v>340879.6023830368</v>
       </c>
       <c r="F110" t="n">
-        <v>341731.3435067562</v>
+        <v>341549.2945976651</v>
       </c>
       <c r="G110" t="n">
-        <v>1.002776205015223</v>
+        <v>1.001964600433545</v>
       </c>
       <c r="H110" t="n">
-        <v>406481.4254356603</v>
+        <v>406710.1778926358</v>
       </c>
       <c r="I110" t="n">
-        <v>416222.0357399932</v>
+        <v>416067.2813404013</v>
       </c>
       <c r="J110" t="n">
-        <v>157655.8948400686</v>
+        <v>157755.2671167935</v>
       </c>
       <c r="K110" t="n">
         <v>94842.71303333271</v>
@@ -10435,22 +10435,22 @@
         <v>419299.32</v>
       </c>
       <c r="E111" t="n">
-        <v>349304.8851205116</v>
+        <v>349299.3285618978</v>
       </c>
       <c r="F111" t="n">
-        <v>350616.3584379319</v>
+        <v>350258.8016099056</v>
       </c>
       <c r="G111" t="n">
-        <v>1.003754523264018</v>
+        <v>1.002746850536352</v>
       </c>
       <c r="H111" t="n">
-        <v>416643.4610715518</v>
+        <v>416755.9192865839</v>
       </c>
       <c r="I111" t="n">
-        <v>427043.8086692331</v>
+        <v>426676.9970145815</v>
       </c>
       <c r="J111" t="n">
-        <v>161597.2922110703</v>
+        <v>161651.8222145783</v>
       </c>
       <c r="K111" t="n">
         <v>94463.25767815557</v>
@@ -10487,22 +10487,22 @@
         <v>429254.35</v>
       </c>
       <c r="E112" t="n">
-        <v>359085.421903886</v>
+        <v>359254.3594259119</v>
       </c>
       <c r="F112" t="n">
-        <v>360784.2328326319</v>
+        <v>360381.2809764318</v>
       </c>
       <c r="G112" t="n">
-        <v>1.004730938169917</v>
+        <v>1.00313683472713</v>
       </c>
       <c r="H112" t="n">
-        <v>428309.4779815552</v>
+        <v>428633.4629862515</v>
       </c>
       <c r="I112" t="n">
-        <v>439428.0791206408</v>
+        <v>439007.9622283029</v>
       </c>
       <c r="J112" t="n">
-        <v>166122.0163929803</v>
+        <v>166258.8991476938</v>
       </c>
       <c r="K112" t="n">
         <v>94420.73460926655</v>
@@ -10539,22 +10539,22 @@
         <v>439600.88</v>
       </c>
       <c r="E113" t="n">
-        <v>369498.8991390986</v>
+        <v>369600.8849773781</v>
       </c>
       <c r="F113" t="n">
-        <v>371246.9755847781</v>
+        <v>370940.4525090413</v>
       </c>
       <c r="G113" t="n">
-        <v>1.004730938169917</v>
+        <v>1.003624362348984</v>
       </c>
       <c r="H113" t="n">
-        <v>440730.4528430203</v>
+        <v>440978.1067202555</v>
       </c>
       <c r="I113" t="n">
-        <v>452171.4934151393</v>
+        <v>451870.8955215922</v>
       </c>
       <c r="J113" t="n">
-        <v>170939.5548683767</v>
+        <v>171047.1554431474</v>
       </c>
       <c r="K113" t="n">
         <v>93961.68422360416</v>
@@ -10591,22 +10591,22 @@
         <v>450319.31</v>
       </c>
       <c r="E114" t="n">
-        <v>380214.3672141324</v>
+        <v>380319.310641722</v>
       </c>
       <c r="F114" t="n">
-        <v>382755.6318279062</v>
+        <v>382365.4184463198</v>
       </c>
       <c r="G114" t="n">
-        <v>1.006683767981715</v>
+        <v>1.005379973478458</v>
       </c>
       <c r="H114" t="n">
-        <v>453511.6359754678</v>
+        <v>453766.4718151429</v>
       </c>
       <c r="I114" t="n">
-        <v>466188.8097110086</v>
+        <v>465788.5191036572</v>
       </c>
       <c r="J114" t="n">
-        <v>175896.8019595596</v>
+        <v>176007.5229509987</v>
       </c>
       <c r="K114" t="n">
         <v>94252.79772593097</v>
@@ -10643,22 +10643,22 @@
         <v>463174.1</v>
       </c>
       <c r="E115" t="n">
-        <v>393141.655699413</v>
+        <v>393174.1033414122</v>
       </c>
       <c r="F115" t="n">
-        <v>395003.8120463992</v>
+        <v>394754.0580039805</v>
       </c>
       <c r="G115" t="n">
-        <v>1.004736604020435</v>
+        <v>1.004018460649216</v>
       </c>
       <c r="H115" t="n">
-        <v>468931.0315986337</v>
+        <v>469103.7785624947</v>
       </c>
       <c r="I115" t="n">
-        <v>481106.8516217609</v>
+        <v>480880.0671226157</v>
       </c>
       <c r="J115" t="n">
-        <v>181877.2932261846</v>
+        <v>181956.5772267424</v>
       </c>
       <c r="K115" t="n">
         <v>95387.73178112155</v>
@@ -10695,22 +10695,22 @@
         <v>473317.99</v>
       </c>
       <c r="E116" t="n">
-        <v>403363.3387475977</v>
+        <v>403317.9952076207</v>
       </c>
       <c r="F116" t="n">
-        <v>405273.9111596055</v>
+        <v>404899.2372946828</v>
       </c>
       <c r="G116" t="n">
-        <v>1.004736604020435</v>
+        <v>1.00392058402018</v>
       </c>
       <c r="H116" t="n">
-        <v>481123.2384201982</v>
+        <v>481206.6560494071</v>
       </c>
       <c r="I116" t="n">
-        <v>493615.6297639267</v>
+        <v>493238.6848476669</v>
       </c>
       <c r="J116" t="n">
-        <v>186606.1028500654</v>
+        <v>186651.0569191924</v>
       </c>
       <c r="K116" t="n">
         <v>96036.64674223015</v>
@@ -10747,22 +10747,22 @@
         <v>481989.33</v>
       </c>
       <c r="E117" t="n">
-        <v>411833.9688612972</v>
+        <v>411989.3321045846</v>
       </c>
       <c r="F117" t="n">
-        <v>414595.2111162764</v>
+        <v>414130.9399050015</v>
       </c>
       <c r="G117" t="n">
-        <v>1.006704746241826</v>
+        <v>1.005198211782516</v>
       </c>
       <c r="H117" t="n">
-        <v>491226.8264270223</v>
+        <v>491552.5991544694</v>
       </c>
       <c r="I117" t="n">
-        <v>504968.789248497</v>
+        <v>504484.5268621937</v>
       </c>
       <c r="J117" t="n">
-        <v>190524.8310099168</v>
+        <v>190664.054642955</v>
       </c>
       <c r="K117" t="n">
         <v>96070.71904337834</v>
@@ -10799,22 +10799,22 @@
         <v>489775.93</v>
       </c>
       <c r="E118" t="n">
-        <v>419658.8142696618</v>
+        <v>419775.9304813612</v>
       </c>
       <c r="F118" t="n">
-        <v>422887.115338602</v>
+        <v>422496.3848910826</v>
       </c>
       <c r="G118" t="n">
-        <v>1.007692680242064</v>
+        <v>1.006480729866055</v>
       </c>
       <c r="H118" t="n">
-        <v>500560.1361291357</v>
+        <v>500842.9432784888</v>
       </c>
       <c r="I118" t="n">
-        <v>515068.1650334669</v>
+        <v>514675.11430481</v>
       </c>
       <c r="J118" t="n">
-        <v>194144.8027991052</v>
+        <v>194267.6052757069</v>
       </c>
       <c r="K118" t="n">
         <v>96288.82564092237</v>
@@ -10851,22 +10851,22 @@
         <v>498633.202123</v>
       </c>
       <c r="E119" t="n">
-        <v>428471.6493693247</v>
+        <v>428633.2026145178</v>
       </c>
       <c r="F119" t="n">
-        <v>432190.6318760513</v>
+        <v>431918.0542741537</v>
       </c>
       <c r="G119" t="n">
-        <v>1.008679646628197</v>
+        <v>1.007663549252833</v>
       </c>
       <c r="H119" t="n">
-        <v>511071.8989878476</v>
+        <v>511410.7293816649</v>
       </c>
       <c r="I119" t="n">
-        <v>526399.6646642032</v>
+        <v>526152.3693538073</v>
       </c>
       <c r="J119" t="n">
-        <v>198221.8436578864</v>
+        <v>198366.6517470242</v>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
@@ -10924,7 +10924,7 @@
         <v>0.1100999858071403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.11</v>
+        <v>0.1101</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -10943,7 +10943,7 @@
         <v>0.08829998274969819</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.0883</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -10962,7 +10962,7 @@
         <v>0.04180000009665052</v>
       </c>
       <c r="D4" t="n">
-        <v>0.042</v>
+        <v>0.0418</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -10981,7 +10981,7 @@
         <v>0.04579999278228919</v>
       </c>
       <c r="D5" t="n">
-        <v>0.046</v>
+        <v>0.0458</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -11000,7 +11000,7 @@
         <v>0.04029998613466979</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>0.0403</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -11019,7 +11019,7 @@
         <v>0.04170001027115888</v>
       </c>
       <c r="D7" t="n">
-        <v>0.042</v>
+        <v>0.0417</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0.03469998595288093</v>
       </c>
       <c r="D8" t="n">
-        <v>0.035</v>
+        <v>0.0347</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -11057,7 +11057,7 @@
         <v>0.0269000035126794</v>
       </c>
       <c r="D9" t="n">
-        <v>0.027</v>
+        <v>0.0269</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -11076,7 +11076,7 @@
         <v>0.02430000050847703</v>
       </c>
       <c r="D10" t="n">
-        <v>0.024</v>
+        <v>0.0243</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -11114,7 +11114,7 @@
         <v>0.02209999395795847</v>
       </c>
       <c r="D12" t="n">
-        <v>0.022</v>
+        <v>0.0221</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -11152,7 +11152,7 @@
         <v>0.03730000175284753</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0373</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -11171,7 +11171,7 @@
         <v>0.02779999199950733</v>
       </c>
       <c r="D15" t="n">
-        <v>0.028</v>
+        <v>0.0278</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -11209,7 +11209,7 @@
         <v>0.01620001423237682</v>
       </c>
       <c r="D17" t="n">
-        <v>0.016</v>
+        <v>0.0162</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -11247,7 +11247,7 @@
         <v>0.01879999751465267</v>
       </c>
       <c r="D19" t="n">
-        <v>0.019</v>
+        <v>0.0188</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -11266,7 +11266,7 @@
         <v>0.02080001132705589</v>
       </c>
       <c r="D20" t="n">
-        <v>0.021</v>
+        <v>0.0208</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>0.02340000562618494</v>
       </c>
       <c r="D21" t="n">
-        <v>0.023</v>
+        <v>0.0234</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
@@ -11304,7 +11304,7 @@
         <v>0.0247000121069143</v>
       </c>
       <c r="D22" t="n">
-        <v>0.025</v>
+        <v>0.0247</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -11323,7 +11323,7 @@
         <v>0.02849999822501803</v>
       </c>
       <c r="D23" t="n">
-        <v>0.028</v>
+        <v>0.0285</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -11342,7 +11342,7 @@
         <v>0.02880001313832392</v>
       </c>
       <c r="D24" t="n">
-        <v>0.029</v>
+        <v>0.0288</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -11380,7 +11380,7 @@
         <v>0.03379999295854841</v>
       </c>
       <c r="D26" t="n">
-        <v>0.034</v>
+        <v>0.0338</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
@@ -11399,7 +11399,7 @@
         <v>0.02579999547274348</v>
       </c>
       <c r="D27" t="n">
-        <v>0.026</v>
+        <v>0.0258</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -11418,7 +11418,7 @@
         <v>0.02150000797137763</v>
       </c>
       <c r="D28" t="n">
-        <v>0.021</v>
+        <v>0.0215</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -11437,7 +11437,7 @@
         <v>0.01890000403651215</v>
       </c>
       <c r="D29" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -11456,7 +11456,7 @@
         <v>0.0210999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.021</v>
+        <v>0.0211</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
@@ -11527,13 +11527,13 @@
         <v>2555298.3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.999099099099099</v>
+        <v>0.999189262228628</v>
       </c>
       <c r="D3" t="n">
-        <v>-2302.070540540801</v>
+        <v>-2071.676848932589</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.09009009009010027</v>
+        <v>-0.08107377713719721</v>
       </c>
     </row>
     <row r="4">
@@ -11546,13 +11546,13 @@
         <v>4202722.9</v>
       </c>
       <c r="C4" t="n">
-        <v>1.003690547164812</v>
+        <v>1.00368804692487</v>
       </c>
       <c r="D4" t="n">
-        <v>15510.34708308401</v>
+        <v>15499.83926742532</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3690547164811653</v>
+        <v>0.3688046924869903</v>
       </c>
     </row>
     <row r="5">
@@ -11565,13 +11565,13 @@
         <v>3010772</v>
       </c>
       <c r="C5" t="n">
-        <v>1.001764077784457</v>
+        <v>1.00156852906805</v>
       </c>
       <c r="D5" t="n">
-        <v>5311.235999264426</v>
+        <v>4722.483399271857</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1764077784456752</v>
+        <v>0.1568529068050273</v>
       </c>
     </row>
     <row r="6">
@@ -11584,13 +11584,13 @@
         <v>3118531.9</v>
       </c>
       <c r="C6" t="n">
-        <v>1.002721787227845</v>
+        <v>1.002909316924902</v>
       </c>
       <c r="D6" t="n">
-        <v>8487.980295047535</v>
+        <v>9072.797637515874</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2721787227845107</v>
+        <v>0.2909316924901706</v>
       </c>
     </row>
     <row r="7">
@@ -11603,13 +11603,13 @@
         <v>3256710.2</v>
       </c>
       <c r="C7" t="n">
-        <v>1.003685942792487</v>
+        <v>1.003584157376548</v>
       </c>
       <c r="D7" t="n">
-        <v>12004.04748890932</v>
+        <v>11672.56188660854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3685942792487129</v>
+        <v>0.3584157376547825</v>
       </c>
     </row>
     <row r="8">
@@ -11622,13 +11622,13 @@
         <v>3334485.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1.003685942792487</v>
+        <v>1.004162203353725</v>
       </c>
       <c r="D8" t="n">
-        <v>12290.72279537858</v>
+        <v>13878.80673104802</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3685942792487351</v>
+        <v>0.4162203353725191</v>
       </c>
     </row>
     <row r="9">
@@ -11641,13 +11641,13 @@
         <v>3505778</v>
       </c>
       <c r="C9" t="n">
-        <v>1.002716197920224</v>
+        <v>1.003871057455391</v>
       </c>
       <c r="D9" t="n">
-        <v>9522.386912367581</v>
+        <v>13571.06806384677</v>
       </c>
       <c r="E9" t="n">
-        <v>0.271619792022415</v>
+        <v>0.3871057455391291</v>
       </c>
     </row>
     <row r="10">
@@ -11660,13 +11660,13 @@
         <v>5335814.7</v>
       </c>
       <c r="C10" t="n">
-        <v>1.001739843297128</v>
+        <v>1.003382270301114</v>
       </c>
       <c r="D10" t="n">
-        <v>9283.481440510017</v>
+        <v>18047.16759205596</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1739843297127619</v>
+        <v>0.338227030111371</v>
       </c>
     </row>
     <row r="11">
@@ -11679,13 +11679,13 @@
         <v>3762351.2</v>
       </c>
       <c r="C11" t="n">
-        <v>1.001739843297128</v>
+        <v>1.002990438896134</v>
       </c>
       <c r="D11" t="n">
-        <v>6545.901516760054</v>
+        <v>11251.08136939783</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1739843297127619</v>
+        <v>0.2990438896134373</v>
       </c>
     </row>
     <row r="12">
@@ -11698,13 +11698,13 @@
         <v>3863750.9</v>
       </c>
       <c r="C12" t="n">
-        <v>1.001739843297128</v>
+        <v>1.003088101061558</v>
       </c>
       <c r="D12" t="n">
-        <v>6722.321105135805</v>
+        <v>11931.65325588393</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1739843297127619</v>
+        <v>0.3088101061557547</v>
       </c>
     </row>
     <row r="13">
@@ -11717,13 +11717,13 @@
         <v>3945383.3</v>
       </c>
       <c r="C13" t="n">
-        <v>1.001739843297128</v>
+        <v>1.003284380897398</v>
       </c>
       <c r="D13" t="n">
-        <v>6864.348689104247</v>
+        <v>12958.14154343273</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1739843297127619</v>
+        <v>0.3284380897397909</v>
       </c>
     </row>
     <row r="14">
@@ -11736,13 +11736,13 @@
         <v>4047468.9</v>
       </c>
       <c r="C14" t="n">
-        <v>1.002718104862847</v>
+        <v>1.004460104781262</v>
       </c>
       <c r="D14" t="n">
-        <v>11001.44489931318</v>
+        <v>18052.13539289933</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2718104862847293</v>
+        <v>0.446010478126202</v>
       </c>
     </row>
     <row r="15">
@@ -11755,13 +11755,13 @@
         <v>4224941.8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9998172810300717</v>
+        <v>1.00116774542885</v>
       </c>
       <c r="D15" t="n">
-        <v>-771.9770137029119</v>
+        <v>4933.656474108735</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0182718969928275</v>
+        <v>0.1167745428850342</v>
       </c>
     </row>
     <row r="16">
@@ -11774,13 +11774,13 @@
         <v>6196115</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9988446961263459</v>
+        <v>0.999901430903595</v>
       </c>
       <c r="D16" t="n">
-        <v>-7158.395661106555</v>
+        <v>-610.7454567717356</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1155303873654145</v>
+        <v>-0.009856909640504341</v>
       </c>
     </row>
     <row r="17">
@@ -11793,13 +11793,13 @@
         <v>4707376.6</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9998287795708054</v>
+        <v>1.000393993184828</v>
       </c>
       <c r="D17" t="n">
-        <v>-805.9990418325991</v>
+        <v>1854.674298821001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01712204291945962</v>
+        <v>0.03939931848284672</v>
       </c>
     </row>
     <row r="18">
@@ -11812,13 +11812,13 @@
         <v>4468820.600000001</v>
       </c>
       <c r="C18" t="n">
-        <v>1.000812863015265</v>
+        <v>1.000689326975377</v>
       </c>
       <c r="D18" t="n">
-        <v>3632.538987592648</v>
+        <v>3080.478587699152</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08128630152646199</v>
+        <v>0.06893269753767139</v>
       </c>
     </row>
     <row r="19">
@@ -11831,13 +11831,13 @@
         <v>4595791.5</v>
       </c>
       <c r="C19" t="n">
-        <v>1.001795014990746</v>
+        <v>1.001278545421094</v>
       </c>
       <c r="D19" t="n">
-        <v>8249.514636842903</v>
+        <v>5875.928178625489</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1795014990745969</v>
+        <v>0.1278545421093513</v>
       </c>
     </row>
     <row r="20">
@@ -11850,13 +11850,13 @@
         <v>4684325.699999999</v>
       </c>
       <c r="C20" t="n">
-        <v>1.001795014990746</v>
+        <v>1.001081985047042</v>
       </c>
       <c r="D20" t="n">
-        <v>8408.434853036602</v>
+        <v>5068.370362872677</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1795014990745969</v>
+        <v>0.10819850470416</v>
       </c>
     </row>
     <row r="21">
@@ -11869,13 +11869,13 @@
         <v>4789901.500000001</v>
       </c>
       <c r="C21" t="n">
-        <v>1.002776205015223</v>
+        <v>1.001964600433545</v>
       </c>
       <c r="D21" t="n">
-        <v>13297.74856672374</v>
+        <v>9410.242563536596</v>
       </c>
       <c r="E21" t="n">
-        <v>0.277620501522291</v>
+        <v>0.1964600433544739</v>
       </c>
     </row>
     <row r="22">
@@ -11888,13 +11888,13 @@
         <v>7386910.4</v>
       </c>
       <c r="C22" t="n">
-        <v>1.002776205015223</v>
+        <v>1.001964600433545</v>
       </c>
       <c r="D22" t="n">
-        <v>20507.57769948227</v>
+        <v>14512.32737439614</v>
       </c>
       <c r="E22" t="n">
-        <v>0.277620501522291</v>
+        <v>0.1964600433544739</v>
       </c>
     </row>
     <row r="23">
@@ -11907,13 +11907,13 @@
         <v>5077070.1</v>
       </c>
       <c r="C23" t="n">
-        <v>1.003754523264018</v>
+        <v>1.002746850536352</v>
       </c>
       <c r="D23" t="n">
-        <v>19061.97780350208</v>
+        <v>13945.9527272836</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3754523264018372</v>
+        <v>0.2746850536352374</v>
       </c>
     </row>
     <row r="24">
@@ -11926,13 +11926,13 @@
         <v>5220469.1</v>
       </c>
       <c r="C24" t="n">
-        <v>1.004730938169917</v>
+        <v>1.00313683472713</v>
       </c>
       <c r="D24" t="n">
-        <v>24697.71653006334</v>
+        <v>16375.74876478736</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4730938169917209</v>
+        <v>0.3136834727129667</v>
       </c>
     </row>
     <row r="25">
@@ -11945,13 +11945,13 @@
         <v>5335179.899999999</v>
       </c>
       <c r="C25" t="n">
-        <v>1.004730938169917</v>
+        <v>1.003624362348984</v>
       </c>
       <c r="D25" t="n">
-        <v>25240.40623228389</v>
+        <v>19336.62515461741</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4730938169916987</v>
+        <v>0.3624362348984222</v>
       </c>
     </row>
     <row r="26">
@@ -11964,13 +11964,13 @@
         <v>5540072.899999999</v>
       </c>
       <c r="C26" t="n">
-        <v>1.006683767981715</v>
+        <v>1.005379973478458</v>
       </c>
       <c r="D26" t="n">
-        <v>37028.56186538508</v>
+        <v>29805.44527072193</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6683767981714661</v>
+        <v>0.5379973478457645</v>
       </c>
     </row>
     <row r="27">
@@ -11983,13 +11983,13 @@
         <v>5677550.100000001</v>
       </c>
       <c r="C27" t="n">
-        <v>1.004736604020435</v>
+        <v>1.004018460649216</v>
       </c>
       <c r="D27" t="n">
-        <v>26892.30662987905</v>
+        <v>22815.0116608034</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4736604020434632</v>
+        <v>0.4018460649216182</v>
       </c>
     </row>
     <row r="28">
@@ -12002,13 +12002,13 @@
         <v>8664734.6</v>
       </c>
       <c r="C28" t="n">
-        <v>1.004736604020435</v>
+        <v>1.00392058402018</v>
       </c>
       <c r="D28" t="n">
-        <v>41041.41674235906</v>
+        <v>33970.82001186388</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4736604020434632</v>
+        <v>0.3920584020180362</v>
       </c>
     </row>
     <row r="29">
@@ -12021,13 +12021,13 @@
         <v>6014065.1</v>
       </c>
       <c r="C29" t="n">
-        <v>1.006704746241826</v>
+        <v>1.005198211782516</v>
       </c>
       <c r="D29" t="n">
-        <v>40322.78037732417</v>
+        <v>31262.38406363963</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6704746241826376</v>
+        <v>0.5198211782516227</v>
       </c>
     </row>
     <row r="30">
@@ -12040,13 +12040,13 @@
         <v>5846619.200000001</v>
       </c>
       <c r="C30" t="n">
-        <v>1.007692680242064</v>
+        <v>1.006480729866055</v>
       </c>
       <c r="D30" t="n">
-        <v>44976.17200271099</v>
+        <v>37890.35966488782</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7692680242063821</v>
+        <v>0.6480729866054524</v>
       </c>
     </row>
   </sheetData>
@@ -12136,7 +12136,7 @@
         <v>30612285.3</v>
       </c>
       <c r="D2" t="n">
-        <v>70108.13147402066</v>
+        <v>84393.04772883977</v>
       </c>
       <c r="E2" t="n">
         <v>6537505.5</v>
@@ -12145,19 +12145,19 @@
         <v>631627.4000000004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2290195938884075</v>
+        <v>0.2756835920670051</v>
       </c>
       <c r="H2" t="n">
-        <v>1.072398814410491</v>
+        <v>1.290905953789863</v>
       </c>
       <c r="I2" t="n">
-        <v>11.09960262553851</v>
+        <v>13.36120752976196</v>
       </c>
       <c r="J2" t="n">
         <v>584377011.02669</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01199707212144569</v>
+        <v>0.01444154135710608</v>
       </c>
       <c r="L2" t="n">
         <v>5.238447906466646</v>
@@ -12174,7 +12174,7 @@
         <v>56673137.4</v>
       </c>
       <c r="D3" t="n">
-        <v>76493.45923734939</v>
+        <v>98317.94394490187</v>
       </c>
       <c r="E3" t="n">
         <v>11769218.7</v>
@@ -12183,19 +12183,19 @@
         <v>1453819.100000002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1349730449850645</v>
+        <v>0.1734824441621647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6499450914048303</v>
+        <v>0.8353820797373903</v>
       </c>
       <c r="I3" t="n">
-        <v>5.261552777601374</v>
+        <v>6.76273574510761</v>
       </c>
       <c r="J3" t="n">
         <v>850239798.2248749</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008996692391611395</v>
+        <v>0.01156355467600663</v>
       </c>
       <c r="L3" t="n">
         <v>6.665547474762039</v>
@@ -12212,7 +12212,7 @@
         <v>47375761</v>
       </c>
       <c r="D4" t="n">
-        <v>259261.3381835077</v>
+        <v>205402.347318605</v>
       </c>
       <c r="E4" t="n">
         <v>12277683.7</v>
@@ -12221,13 +12221,13 @@
         <v>2336619.799999998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5472446937232474</v>
+        <v>0.4335599956243553</v>
       </c>
       <c r="H4" t="n">
-        <v>2.11164698911007</v>
+        <v>1.672973113964527</v>
       </c>
       <c r="I4" t="n">
-        <v>11.09557225285465</v>
+        <v>8.79057634102926</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>

--- a/output/IIJP_resultados.xlsx
+++ b/output/IIJP_resultados.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,19 +464,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ultimo IPC: 2026-08 | ultimo haber: 2026-09 | ultima IMIG: 2026-08 | replicas bootstrap: 500</t>
+          <t>Version del codigo (commit): cd648c2 (2026-10-06)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Niveles base dic-2016 = 100. Variaciones en %. Brechas: (1 + infl. A) / (1 + infl. B) - 1, en %.</t>
+          <t>Ultimo IPC: 2026-08 | ultimo haber: 2026-09 | ultima IMIG: 2026-08 | replicas bootstrap: 500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>Niveles base dic-2016 = 100. Variaciones en %. Brechas: (1 + infl. A) / (1 + infl. B) - 1, en %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Montos fiscales en millones de pesos corrientes. Metodologia: README y docs/ del repo github.com/santiagoriverti/IPC_jubilados.</t>
         </is>

--- a/output/IIJP_resultados.xlsx
+++ b/output/IIJP_resultados.xlsx
@@ -482,14 +482,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Version del codigo (commit): 6e7aab1 (2026-10-13)</t>
+          <t>Version del codigo (commit): f9f5e82 (2026-10-16)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ultimo IPC: 2026-08 | ultimo haber: 2026-09 | ultima IMIG: 2026-08 | replicas bootstrap: 500</t>
+          <t>Ultimo IPC: 2026-09 | ultimo haber: 2026-09 | ultima IMIG: 2026-08 | replicas bootstrap: 500</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15064,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>307.6987290026486</v>
+        <v>315.8687058437218</v>
       </c>
       <c r="D2" t="n">
         <v>0.3223985012981168</v>
@@ -15076,13 +15076,13 @@
         <v>0.2797980904996444</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.06005636785562597</v>
+        <v>-0.07701408388151255</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5212557038747749</v>
+        <v>-0.5144346153475574</v>
       </c>
       <c r="I2" t="n">
-        <v>0.321227134500841</v>
+        <v>0.3000707793517532</v>
       </c>
     </row>
     <row r="3">
@@ -15097,7 +15097,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>284.7738130516393</v>
+        <v>290.2036131476912</v>
       </c>
       <c r="D3" t="n">
         <v>0.01734095434892463</v>
@@ -15109,13 +15109,13 @@
         <v>0.01774816771985328</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0491219236939413</v>
+        <v>0.05265338590619636</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03076122860459552</v>
+        <v>-0.03128250130825934</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08255930807767091</v>
+        <v>0.08657623650085437</v>
       </c>
     </row>
     <row r="4">
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>160.7907706457842</v>
+        <v>164.3952065494663</v>
       </c>
       <c r="D4" t="n">
         <v>0.06713245039436472</v>
@@ -15142,13 +15142,13 @@
         <v>0.08923990062959307</v>
       </c>
       <c r="G4" t="n">
-        <v>1.753440673368511</v>
+        <v>1.763588825043057</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9314117729190887</v>
+        <v>0.9362244307656638</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8699244262833976</v>
+        <v>0.8741005074112491</v>
       </c>
     </row>
     <row r="5">
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>637.8764737078718</v>
+        <v>661.0683232916255</v>
       </c>
       <c r="D5" t="n">
         <v>0.08321117127415475</v>
@@ -15175,13 +15175,13 @@
         <v>0.08112969316366256</v>
       </c>
       <c r="G5" t="n">
-        <v>1.033162470761377</v>
+        <v>1.084707226091788</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5354252777411228</v>
+        <v>-0.5170209149479728</v>
       </c>
       <c r="I5" t="n">
-        <v>1.580840323313186</v>
+        <v>1.613054382773203</v>
       </c>
     </row>
     <row r="6">
@@ -15196,7 +15196,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>235.9072712569337</v>
+        <v>241.446907424159</v>
       </c>
       <c r="D6" t="n">
         <v>0.07197156671799745</v>
@@ -15208,13 +15208,13 @@
         <v>0.06413747610272272</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1548765432223989</v>
+        <v>0.1563966881353237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1333501574224233</v>
+        <v>0.136381313414816</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01279513662901522</v>
+        <v>-0.01371293635349342</v>
       </c>
     </row>
     <row r="7">
@@ -15229,7 +15229,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>355.4437061811902</v>
+        <v>366.2825617050481</v>
       </c>
       <c r="D7" t="n">
         <v>0.1263643306850609</v>
@@ -15241,13 +15241,13 @@
         <v>0.06746882796691347</v>
       </c>
       <c r="G7" t="n">
-        <v>0.201026225595985</v>
+        <v>0.2170857432394483</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2267114784272573</v>
+        <v>-0.2007931908051827</v>
       </c>
       <c r="I7" t="n">
-        <v>0.215733019868951</v>
+        <v>0.2092746980362299</v>
       </c>
     </row>
     <row r="8">
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>399.9708928266783</v>
+        <v>407.6087261670557</v>
       </c>
       <c r="D8" t="n">
         <v>0.1009547118642586</v>
@@ -15274,13 +15274,13 @@
         <v>0.1333086735170171</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4196920833397032</v>
+        <v>0.4159896346158248</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.006408094121821948</v>
+        <v>0.01428360498779435</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5474664591409854</v>
+        <v>0.5198228194939652</v>
       </c>
     </row>
     <row r="9">
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>451.8521617530836</v>
+        <v>465.6916201012843</v>
       </c>
       <c r="D9" t="n">
         <v>0.0345676436650259</v>
@@ -15307,13 +15307,13 @@
         <v>0.03454070577851816</v>
       </c>
       <c r="G9" t="n">
-        <v>0.410389204289822</v>
+        <v>0.4210413051352003</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.007160891095375359</v>
+        <v>-0.006835940546377395</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4177173342343694</v>
+        <v>0.4280291365813487</v>
       </c>
     </row>
     <row r="10">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>301.5901939861159</v>
+        <v>309.0560102247305</v>
       </c>
       <c r="D10" t="n">
         <v>0.08340813423992612</v>
@@ -15340,13 +15340,13 @@
         <v>0.09282467248179964</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3344848431768299</v>
+        <v>-0.4070576371924901</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1893927857588179</v>
+        <v>0.1923738489269353</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4957145697929701</v>
+        <v>-0.571955716883757</v>
       </c>
     </row>
     <row r="11">
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>467.1517260661713</v>
+        <v>484.111302677154</v>
       </c>
       <c r="D11" t="n">
         <v>0.005433507220168736</v>
@@ -15373,13 +15373,13 @@
         <v>0.02331721008531477</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3075759970226092</v>
+        <v>-0.3229464315396724</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3761933236621421</v>
+        <v>-0.3987199582926629</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1496540012210607</v>
+        <v>0.1559731702080562</v>
       </c>
     </row>
     <row r="12">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>382.1698661292928</v>
+        <v>387.2600117463288</v>
       </c>
       <c r="D12" t="n">
         <v>0.05382216872314478</v>
@@ -15406,13 +15406,13 @@
         <v>0.08005515833220121</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.502385456013367</v>
+        <v>-0.472252438935726</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1675616710989229</v>
+        <v>-0.1474279417593886</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2303398770381198</v>
+        <v>-0.2232231525438136</v>
       </c>
     </row>
     <row r="13">
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>421.8398782235168</v>
+        <v>431.7620620273444</v>
       </c>
       <c r="D13" t="n">
         <v>0.03339485956885666</v>
@@ -15439,13 +15439,13 @@
         <v>0.03643142372275936</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2000386815785948</v>
+        <v>0.1937173021315306</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.08300133579194036</v>
+        <v>-0.08111950552417965</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2975156641982205</v>
+        <v>0.28894637251738</v>
       </c>
     </row>
   </sheetData>
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13021.2544</v>
+        <v>13284.1945</v>
       </c>
       <c r="D2" t="n">
         <v>0.275901012166711</v>
@@ -15533,13 +15533,13 @@
         <v>0.2352536315445318</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1759241152181787</v>
+        <v>0.1591004935727382</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3475832712855106</v>
+        <v>0.3547310537420719</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1552761385062998</v>
+        <v>-0.1759601333367664</v>
       </c>
     </row>
     <row r="3">
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8402.120699999999</v>
+        <v>8522.0998</v>
       </c>
       <c r="D3" t="n">
         <v>0.02052507449006398</v>
@@ -15566,13 +15566,13 @@
         <v>0.02113709303857579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4505548494119221</v>
+        <v>0.4542419841296411</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02231611363226149</v>
+        <v>0.0216187520464907</v>
       </c>
       <c r="I3" t="n">
-        <v>0.428094352419268</v>
+        <v>0.4324470533369942</v>
       </c>
     </row>
     <row r="4">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8118.7562</v>
+        <v>8232.349099999999</v>
       </c>
       <c r="D4" t="n">
         <v>0.06006017813956684</v>
@@ -15599,13 +15599,13 @@
         <v>0.07775507737385262</v>
       </c>
       <c r="G4" t="n">
-        <v>1.277922560616635</v>
+        <v>1.288583366380762</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5810211244713195</v>
+        <v>0.5852416783832132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6924886330576953</v>
+        <v>0.6980707679289736</v>
       </c>
     </row>
     <row r="5">
@@ -15620,7 +15620,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13785.4923</v>
+        <v>14221.9207</v>
       </c>
       <c r="D5" t="n">
         <v>0.1157924583917382</v>
@@ -15632,13 +15632,13 @@
         <v>0.1209513712365965</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6714273685180004</v>
+        <v>0.7199489571530564</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4940666374955098</v>
+        <v>0.5165862028860485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.177279695769643</v>
+        <v>0.203365847249714</v>
       </c>
     </row>
     <row r="6">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9693.6862</v>
+        <v>9855.1994</v>
       </c>
       <c r="D6" t="n">
         <v>0.07129079454606005</v>
@@ -15665,13 +15665,13 @@
         <v>0.05891176072958285</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1099474405584466</v>
+        <v>-0.1082054180459118</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1907618958387997</v>
+        <v>-0.1879195182029169</v>
       </c>
       <c r="I6" t="n">
-        <v>0.084702507861798</v>
+        <v>0.08438742860875979</v>
       </c>
     </row>
     <row r="7">
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13763.0483</v>
+        <v>14092.9674</v>
       </c>
       <c r="D7" t="n">
         <v>0.1147736021002521</v>
@@ -15698,13 +15698,13 @@
         <v>0.06459747717322648</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5140729855979691</v>
+        <v>0.5291565414200659</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9410769434471901</v>
+        <v>0.9684699163550324</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4048792515337663</v>
+        <v>-0.4126701757290122</v>
       </c>
     </row>
     <row r="8">
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12865.1212</v>
+        <v>13063.1836</v>
       </c>
       <c r="D8" t="n">
         <v>0.1115848456187467</v>
@@ -15731,13 +15731,13 @@
         <v>0.1401828896114542</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003893778305633945</v>
+        <v>0.001032289818635995</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1137866507432386</v>
+        <v>-0.09397792840958885</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1066394393499138</v>
+        <v>0.08186335428790621</v>
       </c>
     </row>
     <row r="9">
@@ -15752,7 +15752,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11349.4705</v>
+        <v>11636.6026</v>
       </c>
       <c r="D9" t="n">
         <v>0.04806333578199528</v>
@@ -15764,13 +15764,13 @@
         <v>0.04680845158416642</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2031461741412933</v>
+        <v>-0.192930912850214</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.03048826371487449</v>
+        <v>-0.02952766991398278</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1723051733731708</v>
+        <v>-0.1629761353222697</v>
       </c>
     </row>
     <row r="10">
@@ -15785,7 +15785,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10984.103</v>
+        <v>11190.1635</v>
       </c>
       <c r="D10" t="n">
         <v>0.08452445270880295</v>
@@ -15797,13 +15797,13 @@
         <v>0.09023840876252308</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4428009347416281</v>
+        <v>-0.5139913382047376</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01436888551665836</v>
+        <v>-0.01304264874122475</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.430607001866789</v>
+        <v>-0.5035499407934909</v>
       </c>
     </row>
     <row r="11">
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11419.721</v>
+        <v>11764.196</v>
       </c>
       <c r="D11" t="n">
         <v>0.007266958817888245</v>
@@ -15830,13 +15830,13 @@
         <v>0.02968227289047416</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07893422585779657</v>
+        <v>0.06345569624035406</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09290288941104755</v>
+        <v>0.07052711193524062</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02194655457237147</v>
+        <v>-0.01673424623490066</v>
       </c>
     </row>
     <row r="12">
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15096.1764</v>
+        <v>15256.5986</v>
       </c>
       <c r="D12" t="n">
         <v>0.04731303203755056</v>
@@ -15863,13 +15863,13 @@
         <v>0.06873468774804523</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.036866940253809</v>
+        <v>-1.005718109600307</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5161614998294745</v>
+        <v>-0.4972362257403157</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5305758500779754</v>
+        <v>-0.5202294848870037</v>
       </c>
     </row>
     <row r="13">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11811.9027</v>
+        <v>12038.3938</v>
       </c>
       <c r="D13" t="n">
         <v>0.04290425520062398</v>
@@ -15896,13 +15896,13 @@
         <v>0.04574687830697079</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1544644721632242</v>
+        <v>-0.1606559477149981</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.01064325122989355</v>
+        <v>-0.008860520217267045</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.144916209859497</v>
+        <v>-0.1531000754194477</v>
       </c>
     </row>
   </sheetData>
@@ -15982,13 +15982,13 @@
         <v>0.06245088497574119</v>
       </c>
       <c r="F2" t="n">
-        <v>1.503604481489207</v>
+        <v>1.508659118064703</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6633603337605048</v>
+        <v>0.6638232883023718</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8717699098061049</v>
+        <v>0.8756976288950689</v>
       </c>
     </row>
     <row r="3">
@@ -16012,13 +16012,13 @@
         <v>0.02671236069738478</v>
       </c>
       <c r="F3" t="n">
-        <v>1.345906937467809</v>
+        <v>1.394045743183311</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6980612575292665</v>
+        <v>0.7258921673627956</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5980279470475234</v>
+        <v>0.6183376787115805</v>
       </c>
     </row>
     <row r="4">
@@ -16042,13 +16042,13 @@
         <v>0.03056069553834874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3578301442092078</v>
+        <v>0.3670556855848949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02323230756992053</v>
+        <v>0.02456738811219537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3285236716148189</v>
+        <v>0.3364898325164862</v>
       </c>
     </row>
     <row r="5">
@@ -16072,13 +16072,13 @@
         <v>0.01750767553085242</v>
       </c>
       <c r="F5" t="n">
-        <v>0.289258323119557</v>
+        <v>0.2921018745388263</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2121889169032637</v>
+        <v>0.2153526071369154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04178285538954633</v>
+        <v>0.04207087272677398</v>
       </c>
     </row>
     <row r="6">
@@ -16102,13 +16102,13 @@
         <v>0.0196168330183478</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2552672960516944</v>
+        <v>0.2538580096128113</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.04145601217598615</v>
+        <v>-0.04418015255277964</v>
       </c>
       <c r="H6" t="n">
-        <v>0.301025918068151</v>
+        <v>0.3023523648484732</v>
       </c>
     </row>
     <row r="7">
@@ -16132,13 +16132,13 @@
         <v>0.02678901565385188</v>
       </c>
       <c r="F7" t="n">
-        <v>0.247653692383488</v>
+        <v>0.2527459274622574</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2680514391585838</v>
+        <v>0.2724011424632919</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.004027983018523185</v>
+        <v>-0.003780900999916354</v>
       </c>
     </row>
     <row r="8">
@@ -16162,13 +16162,13 @@
         <v>0.01169545278059152</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2160467177497498</v>
+        <v>0.2112971950424141</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06941256975213418</v>
+        <v>-0.06621950083624839</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2950753726794131</v>
+        <v>0.2868183467652032</v>
       </c>
     </row>
     <row r="9">
@@ -16192,13 +16192,13 @@
         <v>0.04671502368762435</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1710189761951483</v>
+        <v>0.1729868414154194</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3044523065514937</v>
+        <v>0.3101534781495836</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08846124198931395</v>
+        <v>-0.09332654631146306</v>
       </c>
     </row>
     <row r="10">
@@ -16222,13 +16222,13 @@
         <v>0.01595347286854541</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1690970036716823</v>
+        <v>0.1712719419658666</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0848193835677746</v>
+        <v>0.0872341299481041</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05566771247239226</v>
+        <v>0.05592650275132877</v>
       </c>
     </row>
     <row r="11">
@@ -16252,13 +16252,13 @@
         <v>0.01079533354044017</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1513494810652126</v>
+        <v>0.1562304991330768</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1293528863146671</v>
+        <v>0.1345375024819767</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002198604807431403</v>
+        <v>0.00211119281484311</v>
       </c>
     </row>
     <row r="12">
@@ -16282,13 +16282,13 @@
         <v>0.004394768454966399</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1356732016571295</v>
+        <v>0.1334652951435127</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07332021882863206</v>
+        <v>0.0721487018107199</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06736243334543759</v>
+        <v>0.06626619655335293</v>
       </c>
     </row>
     <row r="13">
@@ -16312,13 +16312,13 @@
         <v>0.03619859227242817</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1290646343796054</v>
+        <v>0.1304405616535378</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1458244368298807</v>
+        <v>0.1475324605179831</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.01056149135824467</v>
+        <v>-0.01108342492720378</v>
       </c>
     </row>
     <row r="14">
@@ -16342,13 +16342,13 @@
         <v>0.04690182341731619</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09881276410198742</v>
+        <v>0.09285702431982096</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.318016795989457</v>
+        <v>-0.3027126312210193</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4731055811182279</v>
+        <v>0.4501295564066797</v>
       </c>
     </row>
     <row r="15">
@@ -16372,43 +16372,43 @@
         <v>0.01096492461948334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08256764622733134</v>
+        <v>0.0847537263184103</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.03056506385877304</v>
+        <v>-0.03122610141815417</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1108385101229936</v>
+        <v>0.1137569503888743</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>09.5</t>
+          <t>09.4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Periódicos, diarios, revistas, libros y artículos de papelería</t>
+          <t>Servicios recreativos y culturales</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007505405740507832</v>
+        <v>0.02494574894862498</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01841084832747346</v>
+        <v>0.02150323120024094</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01184660988915939</v>
+        <v>0.02541697191013348</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07201605853657811</v>
+        <v>0.07158652817388469</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04364209356903263</v>
+        <v>-0.004031469462092797</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04299264584402545</v>
+        <v>0.07749378386532146</v>
       </c>
     </row>
     <row r="17">
@@ -16432,43 +16432,43 @@
         <v>0.04602066727046464</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06123241334973175</v>
+        <v>0.06173511154750089</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.06436113207576985</v>
+        <v>-0.06378212249322589</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1183578029668674</v>
+        <v>0.1184087548836531</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>09.4</t>
+          <t>09.5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Servicios recreativos y culturales</t>
+          <t>Periódicos, diarios, revistas, libros y artículos de papelería</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02494574894862498</v>
+        <v>0.007505405740507832</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02150323120024094</v>
+        <v>0.01841084832747346</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02541697191013348</v>
+        <v>0.01184660988915939</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05604827331329269</v>
+        <v>0.05802426094538706</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.008914161513970779</v>
+        <v>0.03809457208475116</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06706032105390797</v>
+        <v>0.03445178344058739</v>
       </c>
     </row>
     <row r="19">
@@ -16492,223 +16492,223 @@
         <v>0.003980010240169429</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05255906008061417</v>
+        <v>0.05398561955030544</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.03039319866529589</v>
+        <v>-0.03140332865857276</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08919366261955049</v>
+        <v>0.09153930406486249</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>01.1.2</t>
+          <t>05.6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carnes y derivados</t>
+          <t>Bienes y servicios para la conservación del hogar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1151350878838685</v>
+        <v>0.03888684433202363</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1024801633537182</v>
+        <v>0.03009800937408675</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0995264845109063</v>
+        <v>0.02793888383029455</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03949871167792149</v>
+        <v>0.02595612648178589</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005453128430790276</v>
+        <v>-0.01115114710316714</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.02459387369376249</v>
+        <v>-0.002629511426289638</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>05.6</t>
+          <t>04.3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bienes y servicios para la conservación del hogar</t>
+          <t>Mantenimiento y reparación de la vivienda</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03888684433202363</v>
+        <v>0.005639212535284059</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03009800937408675</v>
+        <v>0.006960272112938722</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02793888383029455</v>
+        <v>0.006095401628579389</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02581190884279344</v>
+        <v>0.02310123900796111</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.01247427940745741</v>
+        <v>0.009308809340715381</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.002233645270770556</v>
+        <v>0.01512390516526643</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>04.3</t>
+          <t>01.1.2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mantenimiento y reparación de la vivienda</t>
+          <t>Carnes y derivados</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.005639212535284059</v>
+        <v>0.1151350878838685</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006960272112938722</v>
+        <v>0.1024801633537182</v>
       </c>
       <c r="E22" t="n">
-        <v>0.006095401628579389</v>
+        <v>0.0995264845109063</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02398093778133125</v>
+        <v>0.02152313357930247</v>
       </c>
       <c r="G22" t="n">
-        <v>0.009628516013369032</v>
+        <v>-0.014063780784146</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01569982582553344</v>
+        <v>-0.0211334393687879</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>01.2.2</t>
+          <t>11.r</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aguas minerales, bebidas gaseosas y jugos</t>
+          <t>Resto de Restaurantes y hoteles</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01833393237399602</v>
+        <v>0.003162948630840112</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02263558550773363</v>
+        <v>0.003691511092783677</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0188891414590775</v>
+        <v>0.004136583911535006</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01256001809093264</v>
+        <v>0.01789749500727549</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005132541574079543</v>
+        <v>0.02532931536513037</v>
       </c>
       <c r="H23" t="n">
-        <v>0.009313910195555351</v>
+        <v>-0.004790357259031047</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>11.r</t>
+          <t>01.2.2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resto de Restaurantes y hoteles</t>
+          <t>Aguas minerales, bebidas gaseosas y jugos</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.003162948630840112</v>
+        <v>0.01833393237399602</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003691511092783677</v>
+        <v>0.02263558550773363</v>
       </c>
       <c r="E24" t="n">
-        <v>0.004136583911535006</v>
+        <v>0.0188891414590775</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01244889634461554</v>
+        <v>0.01466259867330047</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0172934610285071</v>
+        <v>0.005743025617409605</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.001846911052455256</v>
+        <v>0.01074490626711236</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>01.1.r</t>
+          <t>01.1.4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Resto de Alimentos</t>
+          <t>Leche, productos lácteos y huevos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01219323068062448</v>
+        <v>0.0365245153818896</v>
       </c>
       <c r="D25" t="n">
-        <v>0.007799257212791733</v>
+        <v>0.03931838475528262</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01076510427764652</v>
+        <v>0.03272869977708298</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01058975466842948</v>
+        <v>0.008724473934413208</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.002286809205091257</v>
+        <v>-0.03840640337351845</v>
       </c>
       <c r="H25" t="n">
-        <v>0.007615574549382385</v>
+        <v>0.03462013340027452</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>01.1.4</t>
+          <t>01.1.r</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Leche, productos lácteos y huevos</t>
+          <t>Resto de Alimentos</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0365245153818896</v>
+        <v>0.01219323068062448</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03931838475528262</v>
+        <v>0.007799257212791733</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03272869977708298</v>
+        <v>0.01076510427764652</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007082573021637571</v>
+        <v>0.007413613173985155</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.03580175451264873</v>
+        <v>-0.003194506756406939</v>
       </c>
       <c r="H26" t="n">
-        <v>0.03001394011164279</v>
+        <v>0.005488383990612502</v>
       </c>
     </row>
     <row r="27">
@@ -16732,13 +16732,13 @@
         <v>0.005417686212362112</v>
       </c>
       <c r="F27" t="n">
-        <v>0.006348510333641528</v>
+        <v>0.006031422103075887</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01568176140089485</v>
+        <v>0.01449237197627775</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.01531402562172979</v>
+        <v>-0.01427536975241148</v>
       </c>
     </row>
     <row r="28">
@@ -16762,13 +16762,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.002182499495815876</v>
+        <v>0.002183779516096593</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.002182499495815876</v>
+        <v>0.002183779516096593</v>
       </c>
     </row>
     <row r="29">
@@ -16792,13 +16792,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4.295621433208714e-18</v>
+        <v>4.413178487579569e-18</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.295621433208714e-18</v>
+        <v>4.413178487579569e-18</v>
       </c>
     </row>
     <row r="30">
@@ -16855,10 +16855,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>8.487127214050365e-08</v>
+        <v>5.987764383540419e-07</v>
       </c>
       <c r="H31" t="n">
-        <v>5.288074559819111e-06</v>
+        <v>4.64505857949055e-06</v>
       </c>
     </row>
     <row r="32">
@@ -16882,13 +16882,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0009125102280107116</v>
+        <v>-0.0009042445530697998</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0009125102280107116</v>
+        <v>-0.0009042445530697998</v>
       </c>
     </row>
     <row r="33">
@@ -16912,13 +16912,13 @@
         <v>0.007918613305477818</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.01077888662327894</v>
+        <v>-0.005308510608154935</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.03058232406389293</v>
+        <v>-0.02726593190878854</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01051975960157912</v>
+        <v>0.01274265683927778</v>
       </c>
     </row>
     <row r="34">
@@ -16942,13 +16942,13 @@
         <v>0.02917581932166321</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01364013533911625</v>
+        <v>-0.009156124617720071</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1277945790103508</v>
+        <v>-0.08719789112178307</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09108721360992765</v>
+        <v>0.05395927024805657</v>
       </c>
     </row>
     <row r="35">
@@ -16972,13 +16972,13 @@
         <v>0.02473597094216784</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.01600803617115499</v>
+        <v>-0.01757989291088352</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.01358876603980617</v>
+        <v>-0.01490000468793125</v>
       </c>
       <c r="H35" t="n">
-        <v>0.002440291518807406</v>
+        <v>0.002128025752176781</v>
       </c>
     </row>
     <row r="36">
@@ -17002,13 +17002,13 @@
         <v>0.007426711591527822</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.02866104847839489</v>
+        <v>-0.02912411533169954</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.05968609385079267</v>
+        <v>-0.06034284914851117</v>
       </c>
       <c r="H36" t="n">
-        <v>0.02457109706141541</v>
+        <v>0.0249213194161251</v>
       </c>
     </row>
     <row r="37">
@@ -17032,13 +17032,13 @@
         <v>0.006783243100369942</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.03344572253339006</v>
+        <v>-0.03210034041221395</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.000196164745822485</v>
+        <v>-5.639989010516552e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.0282792020453227</v>
+        <v>-0.02718071388801993</v>
       </c>
     </row>
     <row r="38">
@@ -17062,73 +17062,73 @@
         <v>0.01597736368826727</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.05656237360235123</v>
+        <v>-0.05568593735593318</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.03486223134064455</v>
+        <v>-0.03447668649577131</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.02500786353421017</v>
+        <v>-0.02446322727282157</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>01.1.6</t>
+          <t>07.2.r</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frutas</t>
+          <t>Resto de Funcionamiento de equipos de transporte personal</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0211841127014901</v>
+        <v>0.01536438810458123</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01768654626324203</v>
+        <v>0.01309565504459324</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01386897637901638</v>
+        <v>0.02007499339372879</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.09850479157805805</v>
+        <v>-0.102807996179157</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2227306201565139</v>
+        <v>0.05102291061200966</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1051780707811926</v>
+        <v>-0.1384283108966548</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>07.2.r</t>
+          <t>01.1.6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Resto de Funcionamiento de equipos de transporte personal</t>
+          <t>Frutas</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01536438810458123</v>
+        <v>0.0211841127014901</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01309565504459324</v>
+        <v>0.01768654626324203</v>
       </c>
       <c r="E40" t="n">
-        <v>0.02007499339372879</v>
+        <v>0.01386897637901638</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1044944427811162</v>
+        <v>-0.1031382595877378</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04861240749212754</v>
+        <v>-0.2332063715443203</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1372912878280689</v>
+        <v>0.1117954024813605</v>
       </c>
     </row>
     <row r="41">
@@ -17152,13 +17152,13 @@
         <v>0.03916581889562089</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.2395815785887845</v>
+        <v>-0.2312466304324548</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5682532816451881</v>
+        <v>-0.5506833004240748</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1717515596719733</v>
+        <v>0.1650926324946128</v>
       </c>
     </row>
     <row r="42">
@@ -17182,73 +17182,73 @@
         <v>0.02331721008531477</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.3075759970226092</v>
+        <v>-0.3229464315396724</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.3761933236621421</v>
+        <v>-0.3987199582926629</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1496540012210607</v>
+        <v>0.1559731702080562</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>04.1.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alquiler de la vivienda</t>
+          <t>Restaurantes y comidas fuera del hogar</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01108200060530445</v>
+        <v>0.05065922009230466</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01590261197793738</v>
+        <v>0.09684172302496984</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02444984466367516</v>
+        <v>0.07591857442066621</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.4950435215361664</v>
+        <v>-0.4901499339430015</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.29735211078764</v>
+        <v>-0.1727572571245189</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9009250783661574</v>
+        <v>-0.2184327952847825</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>04.1.1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Restaurantes y comidas fuera del hogar</t>
+          <t>Alquiler de la vivienda</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.05065922009230466</v>
+        <v>0.01108200060530445</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09684172302496984</v>
+        <v>0.01590261197793738</v>
       </c>
       <c r="E44" t="n">
-        <v>0.07591857442066621</v>
+        <v>0.02444984466367516</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5148343523579826</v>
+        <v>-0.4984031874571954</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.18485513212743</v>
+        <v>-1.312190089690799</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.2284929659856645</v>
+        <v>0.9109236393057494</v>
       </c>
     </row>
     <row r="45">
@@ -17272,13 +17272,13 @@
         <v>0.05116632222754036</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.5982223766838302</v>
+        <v>-0.6701337214552746</v>
       </c>
       <c r="G45" t="n">
-        <v>0.081344634875124</v>
+        <v>0.08616204449355699</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.6731299700363411</v>
+        <v>-0.7501674807430189</v>
       </c>
     </row>
   </sheetData>
@@ -17340,61 +17340,61 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>03.1</t>
+          <t>04.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prendas de vestir y materiales</t>
+          <t>Electricidad, gas y otros combustibles</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.04066367098470437</v>
+        <v>0.04250717080752719</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07227342066538996</v>
+        <v>0.02878980866267668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05200450045570493</v>
+        <v>0.03381916515170894</v>
       </c>
       <c r="F2" t="n">
-        <v>1.007466567210577</v>
+        <v>1.026367401462084</v>
       </c>
       <c r="G2" t="n">
-        <v>0.354745976061045</v>
+        <v>0.653830303610796</v>
       </c>
       <c r="H2" t="n">
-        <v>0.649826900885964</v>
+        <v>0.3793141107276312</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>04.5</t>
+          <t>03.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Electricidad, gas y otros combustibles</t>
+          <t>Prendas de vestir y materiales</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04250717080752719</v>
+        <v>0.04066367098470437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02878980866267668</v>
+        <v>0.07227342066538996</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03381916515170894</v>
+        <v>0.05200450045570493</v>
       </c>
       <c r="F3" t="n">
-        <v>0.98053938162146</v>
+        <v>1.012733294791165</v>
       </c>
       <c r="G3" t="n">
-        <v>0.622907591730959</v>
+        <v>0.3549826123578052</v>
       </c>
       <c r="H3" t="n">
-        <v>0.363170525419943</v>
+        <v>0.6542830179407099</v>
       </c>
     </row>
     <row r="4">
@@ -17418,13 +17418,13 @@
         <v>0.02672666298842284</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5323573863604194</v>
+        <v>0.5402149145849703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9824491701342007</v>
+        <v>1.000764465200864</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.433871509335706</v>
+        <v>-0.4410245018386204</v>
       </c>
     </row>
     <row r="5">
@@ -17448,13 +17448,13 @@
         <v>0.01012084601021324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3510632334713112</v>
+        <v>0.3524265825505769</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05908826739961758</v>
+        <v>0.05921448049637022</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2915299095274183</v>
+        <v>0.2926791666551469</v>
       </c>
     </row>
     <row r="6">
@@ -17478,13 +17478,13 @@
         <v>0.02575057691814769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2690336188610576</v>
+        <v>0.2744264170243166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2262751484102745</v>
+        <v>0.230259066025408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04123935762673141</v>
+        <v>0.04236409542298318</v>
       </c>
     </row>
     <row r="7">
@@ -17508,13 +17508,13 @@
         <v>0.08320077750246767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1691082177083119</v>
+        <v>0.1536349305923006</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3067913193923076</v>
+        <v>0.2842536122086827</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.130875411558415</v>
+        <v>-0.1225584951115831</v>
       </c>
     </row>
     <row r="8">
@@ -17538,13 +17538,13 @@
         <v>0.03312286535473784</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1340600218499833</v>
+        <v>0.132400824345379</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05087431954605164</v>
+        <v>0.04853190276415791</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08306083784174786</v>
+        <v>0.08370881857766546</v>
       </c>
     </row>
     <row r="9">
@@ -17568,13 +17568,13 @@
         <v>0.003923112516067247</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1077393293963118</v>
+        <v>0.105509733562697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04976162438959007</v>
+        <v>0.04862058735720635</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05749380376703746</v>
+        <v>0.05630400663301112</v>
       </c>
     </row>
     <row r="10">
@@ -17598,13 +17598,13 @@
         <v>0.01101624702836256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09949161594061091</v>
+        <v>0.1018154015790642</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.03677215376735608</v>
+        <v>-0.03759572844987952</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1365644428918497</v>
+        <v>0.1397678866818473</v>
       </c>
     </row>
     <row r="11">
@@ -17628,13 +17628,13 @@
         <v>0.02968227289047416</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07893422585779657</v>
+        <v>0.06345569624035406</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09290288941104755</v>
+        <v>0.07052711193524062</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.02194655457237147</v>
+        <v>-0.01673424623490066</v>
       </c>
     </row>
     <row r="12">
@@ -17658,13 +17658,13 @@
         <v>0.02606041988301881</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05092458750277368</v>
+        <v>0.05257702830371283</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02940680133652286</v>
+        <v>0.03078974775766984</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02105641708576319</v>
+        <v>0.02124038456197174</v>
       </c>
     </row>
     <row r="13">
@@ -17688,73 +17688,73 @@
         <v>0.0191782437653132</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03781390969487564</v>
+        <v>0.04003318705146346</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003725050441733163</v>
+        <v>0.004215103329876338</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03405046195736101</v>
+        <v>0.03577423735916214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>04.1.1</t>
+          <t>04.r</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alquiler de la vivienda</t>
+          <t>Resto de Vivienda, agua, electricidad, gas y otros combustibles</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02374477879520703</v>
+        <v>0.02567014935395119</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03429196798823585</v>
+        <v>0.01374855520490866</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05073605805100177</v>
+        <v>0.01769307799994329</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03770713840079226</v>
+        <v>0.03420933176655087</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1162875037878666</v>
+        <v>0.02945885222176813</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08817049194160551</v>
+        <v>0.008432077404389789</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>04.r</t>
+          <t>04.1.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Resto de Vivienda, agua, electricidad, gas y otros combustibles</t>
+          <t>Alquiler de la vivienda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02567014935395119</v>
+        <v>0.02374477879520703</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01374855520490866</v>
+        <v>0.03429196798823585</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01769307799994329</v>
+        <v>0.05073605805100177</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03213653596086748</v>
+        <v>0.03403267346085628</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02686796707738609</v>
+        <v>0.1018924809549624</v>
       </c>
       <c r="H15" t="n">
-        <v>0.008330229030876756</v>
+        <v>-0.07941973210042155</v>
       </c>
     </row>
     <row r="16">
@@ -17778,13 +17778,13 @@
         <v>0.0611765359544031</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02743632569277272</v>
+        <v>0.02235890620242868</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08549028294791233</v>
+        <v>0.09973995398188644</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06325793702695789</v>
+        <v>-0.08355572717023188</v>
       </c>
     </row>
     <row r="17">
@@ -17808,73 +17808,73 @@
         <v>0.003952239306187773</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01409999006306116</v>
+        <v>0.01998980443942191</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01298094684938474</v>
+        <v>0.0204537872077669</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0008444829853936388</v>
+        <v>-0.0007598424259050193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>01.1.7</t>
+          <t>06.r</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verduras, tubérculos y legumbres</t>
+          <t>Resto de Salud</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02743114299395998</v>
+        <v>0.02089389485395238</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02662858501489001</v>
+        <v>0.01599769032584188</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0213461001568786</v>
+        <v>0.01498890381255267</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01399193723255938</v>
+        <v>0.01725225029125541</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07778437931855166</v>
+        <v>-0.01069286059308422</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.06124424163356149</v>
+        <v>0.03052574579579716</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>06.r</t>
+          <t>01.1.7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Resto de Salud</t>
+          <t>Verduras, tubérculos y legumbres</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02089389485395238</v>
+        <v>0.02743114299395998</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01599769032584188</v>
+        <v>0.02662858501489001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01498890381255267</v>
+        <v>0.0213461001568786</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01270967237491197</v>
+        <v>0.01464881282191615</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.01634642185181252</v>
+        <v>0.1233560477661225</v>
       </c>
       <c r="H19" t="n">
-        <v>0.03118793204307226</v>
+        <v>-0.1054498289698248</v>
       </c>
     </row>
     <row r="20">
@@ -17898,13 +17898,13 @@
         <v>0.02817159445961436</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005594513264539783</v>
+        <v>0.003998950252011779</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0007621133105780933</v>
+        <v>-0.0004727350043017811</v>
       </c>
       <c r="H20" t="n">
-        <v>0.004580371083383678</v>
+        <v>0.00416407765536456</v>
       </c>
     </row>
     <row r="21">
@@ -17928,13 +17928,13 @@
         <v>0.005244021042044591</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0035318426172241</v>
+        <v>0.003321695231221237</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02102965725604784</v>
+        <v>0.01971573585713626</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01683937324058709</v>
+        <v>-0.01561060334654105</v>
       </c>
     </row>
     <row r="22">
@@ -17958,13 +17958,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.001422374544999847</v>
+        <v>0.001423654565280565</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001422374544999847</v>
+        <v>0.001423654565280565</v>
       </c>
     </row>
     <row r="23">
@@ -17988,13 +17988,13 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.230985875769672e-17</v>
+        <v>1.242741581206758e-17</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.230985875769672e-17</v>
+        <v>1.242741581206758e-17</v>
       </c>
     </row>
     <row r="24">
@@ -18051,70 +18051,70 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.133423624949935e-06</v>
+        <v>-4.619518458736371e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>4.600545407469407e-06</v>
+        <v>3.983035227988813e-06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>07.r</t>
+          <t>01.1.1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resto de Transporte</t>
+          <t>Pan y cereales</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.04201879601664005</v>
       </c>
       <c r="D26" t="n">
-        <v>4.465503238239222e-05</v>
+        <v>0.04749747004766201</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.03894332137650685</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.023728009381779e-05</v>
+        <v>-6.694359608675817e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.02081493020644764</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.023728009381779e-05</v>
+        <v>0.02202419223116643</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>01.1.1</t>
+          <t>07.r</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pan y cereales</t>
+          <t>Resto de Transporte</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.04201879601664005</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04749747004766201</v>
+        <v>4.465503238239222e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03894332137650685</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0006032437026963782</v>
+        <v>-7.197160515290499e-05</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02141953466438386</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02187868840215299</v>
+        <v>-7.197160515290499e-05</v>
       </c>
     </row>
     <row r="28">
@@ -18138,13 +18138,13 @@
         <v>0.01156708411667748</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.004079821515901963</v>
+        <v>-0.003259048892175446</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.002009073403489504</v>
+        <v>-0.001530814706683717</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.001636928871190613</v>
+        <v>-0.001206078722705547</v>
       </c>
     </row>
     <row r="29">
@@ -18168,13 +18168,13 @@
         <v>0.004619276756425525</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.004163840850394567</v>
+        <v>-0.005108851987005099</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00101218461282271</v>
+        <v>-0.001240229858440817</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.003246975940086432</v>
+        <v>-0.003983898539661141</v>
       </c>
     </row>
     <row r="30">
@@ -18198,13 +18198,13 @@
         <v>0.01066480075930639</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.006221556201970038</v>
+        <v>-0.009293245174943674</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.002938357616505982</v>
+        <v>-0.003959692995936428</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.002657601578499322</v>
+        <v>-0.00458818379403009</v>
       </c>
     </row>
     <row r="31">
@@ -18228,73 +18228,73 @@
         <v>0.006166670076519014</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.009271594701486707</v>
+        <v>-0.009696991586568131</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.01964353494997435</v>
+        <v>-0.020336080763564</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01107548442216302</v>
+        <v>0.01147935760557251</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>01.1.6</t>
+          <t>01.1.4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frutas</t>
+          <t>Leche, productos lácteos y huevos</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01584557855134778</v>
+        <v>0.03290080521099725</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01347483084533874</v>
+        <v>0.0360716758224468</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01015199900564264</v>
+        <v>0.02878922991449468</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.01244709919490255</v>
+        <v>-0.01370940879305535</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.02635256729187807</v>
+        <v>0.007370382827241449</v>
       </c>
       <c r="H32" t="n">
-        <v>0.01592165552375511</v>
+        <v>-0.01921698356263997</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>01.1.4</t>
+          <t>01.1.6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leche, productos lácteos y huevos</t>
+          <t>Frutas</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.03290080521099725</v>
+        <v>0.01584557855134778</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0360716758224468</v>
+        <v>0.01347483084533874</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02878922991449468</v>
+        <v>0.01015199900564264</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0158984767178347</v>
+        <v>-0.01651249408133382</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01062106622672701</v>
+        <v>-0.03753369005589691</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.02495347247488595</v>
+        <v>0.02338826993942918</v>
       </c>
     </row>
     <row r="34">
@@ -18318,13 +18318,13 @@
         <v>0.005208032037595537</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.02210896645702689</v>
+        <v>-0.02071461595860189</v>
       </c>
       <c r="G34" t="n">
-        <v>0.009462201920410182</v>
+        <v>0.00849897911055026</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.03216274699669139</v>
+        <v>-0.0299270179962839</v>
       </c>
     </row>
     <row r="35">
@@ -18348,13 +18348,13 @@
         <v>0.01580172323950059</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.02313257647099144</v>
+        <v>-0.02139115487750273</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.028707160059657</v>
+        <v>-0.02634657636583946</v>
       </c>
       <c r="H35" t="n">
-        <v>0.004110217775363982</v>
+        <v>0.003210566895225289</v>
       </c>
     </row>
     <row r="36">
@@ -18378,13 +18378,13 @@
         <v>0.02288191037225096</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.03099407313736222</v>
+        <v>-0.02831062345615989</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.02502580483519822</v>
+        <v>-0.02160168825274793</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.002195674241132562</v>
+        <v>-0.002171419686188969</v>
       </c>
     </row>
     <row r="37">
@@ -18408,13 +18408,13 @@
         <v>0.009710415141844298</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.08438527944138584</v>
+        <v>-0.09851782188596503</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.03117435753254676</v>
+        <v>-0.03652930965555892</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.05460304187713207</v>
+        <v>-0.06368110520031808</v>
       </c>
     </row>
     <row r="38">
@@ -18438,13 +18438,13 @@
         <v>0.03008176506281265</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1343897554860368</v>
+        <v>-0.1322643142465161</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2214440931775455</v>
+        <v>-0.2159032087897937</v>
       </c>
       <c r="H38" t="n">
-        <v>0.08280655803985366</v>
+        <v>0.07857166759040025</v>
       </c>
     </row>
     <row r="39">
@@ -18468,73 +18468,73 @@
         <v>0.03325641453127276</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1596174414303293</v>
+        <v>-0.1449976768059171</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.05514273498698562</v>
+        <v>-0.04902932869766053</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1044361657491734</v>
+        <v>-0.09589493879647909</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>12.r</t>
+          <t>05.6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Resto de Bienes y servicios varios</t>
+          <t>Bienes y servicios para la conservación del hogar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01541905326538532</v>
+        <v>0.04676701513222591</v>
       </c>
       <c r="D40" t="n">
-        <v>0.005748011752165567</v>
+        <v>0.03680433803160219</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01757528384735644</v>
+        <v>0.03285134084656404</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.160058985427764</v>
+        <v>-0.1607824463496247</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.01140536454047165</v>
+        <v>-0.2187092659605867</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1494965809428807</v>
+        <v>0.06314704404678806</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>05.6</t>
+          <t>12.r</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bienes y servicios para la conservación del hogar</t>
+          <t>Resto de Bienes y servicios varios</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.04676701513222591</v>
+        <v>0.01541905326538532</v>
       </c>
       <c r="D41" t="n">
-        <v>0.03680433803160219</v>
+        <v>0.005748011752165567</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03285134084656404</v>
+        <v>0.01757528384735644</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.1608720280612203</v>
+        <v>-0.1646548979670099</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2201686971753225</v>
+        <v>-0.008387785212965262</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06364609077603482</v>
+        <v>-0.1572641530748123</v>
       </c>
     </row>
     <row r="42">
@@ -18558,73 +18558,73 @@
         <v>0.04160041954657089</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1810372076842664</v>
+        <v>-0.1722162968916122</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.03995046563528468</v>
+        <v>-0.03802664902453304</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1401424263764794</v>
+        <v>-0.1330491173259858</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>09.r</t>
+          <t>04.1.r</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Resto de Recreación y cultura</t>
+          <t>Resto de Alquiler de la vivienda y gastos conexos</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0422177111215043</v>
+        <v>0.01949767859242419</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02197636979561582</v>
+        <v>0.01171470329378316</v>
       </c>
       <c r="E43" t="n">
-        <v>0.04334846657333877</v>
+        <v>0.01408379327751697</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.3065375432662248</v>
+        <v>-0.3695515975494297</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02218658261328396</v>
+        <v>-0.2673552040430373</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.329061598007521</v>
+        <v>-0.1009767102422243</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>04.1.r</t>
+          <t>09.r</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Resto de Alquiler de la vivienda y gastos conexos</t>
+          <t>Resto de Recreación y cultura</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01949767859242419</v>
+        <v>0.0422177111215043</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01171470329378316</v>
+        <v>0.02197636979561582</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01408379327751697</v>
+        <v>0.04334846657333877</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3747918466147248</v>
+        <v>-0.3759855730755525</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2709842404878791</v>
+        <v>0.02389540225478834</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1028035907994849</v>
+        <v>-0.4002779034297048</v>
       </c>
     </row>
     <row r="45">
@@ -18648,13 +18648,13 @@
         <v>0.06478244844185746</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.05096693031687</v>
+        <v>-1.025707914039729</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.5291424466788592</v>
+        <v>-0.5176900129480826</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.531420333063369</v>
+        <v>-0.5194696424610987</v>
       </c>
     </row>
   </sheetData>
@@ -18668,7 +18668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23767,6 +23767,49 @@
       </c>
       <c r="M118" t="n">
         <v>0.0398388925275872</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.292350558849563</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.01406550748790046</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.0391640213996385</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.1343039032137077</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.0564835267836851</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.128992496655816</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.1159793360425668</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.0434289379443962</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.07151541815630631</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.006978775735763212</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.05697447099999812</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.03976304673065827</v>
       </c>
     </row>
   </sheetData>
@@ -23780,7 +23823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26031,6 +26074,25 @@
       </c>
       <c r="E118" t="n">
         <v>12743.5949867737</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12514.1508</v>
+      </c>
+      <c r="C119" t="n">
+        <v>12455.8215255118</v>
+      </c>
+      <c r="D119" t="n">
+        <v>12665.90268236841</v>
+      </c>
+      <c r="E119" t="n">
+        <v>13014.82550712655</v>
       </c>
     </row>
   </sheetData>
@@ -26167,7 +26229,7 @@
         <v>5350</v>
       </c>
       <c r="G2" t="n">
-        <v>1.203376168781634</v>
+        <v>1.212642270288233</v>
       </c>
       <c r="H2" t="n">
         <v>3.216877010413599</v>
@@ -26176,13 +26238,13 @@
         <v>-4.857384674978816</v>
       </c>
       <c r="J2" t="n">
-        <v>3.055031625224136</v>
+        <v>3.064467262847659</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5159451667158033</v>
+        <v>0.5251483275806601</v>
       </c>
       <c r="L2" t="n">
-        <v>1.602756532869787</v>
+        <v>1.68661020412284</v>
       </c>
       <c r="M2" t="n">
         <v>2.910578865132196</v>
@@ -26191,19 +26253,19 @@
         <v>-0.5745330207206467</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7003242883177885</v>
+        <v>-0.6183713704363991</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9311665426297688</v>
+        <v>-0.8494041409426778</v>
       </c>
       <c r="Q2" t="n">
         <v>1.096065848739647</v>
       </c>
       <c r="R2" t="n">
-        <v>1.586978170777953</v>
+        <v>1.942943164368582</v>
       </c>
       <c r="S2" t="n">
-        <v>34.78276900944921</v>
+        <v>34.60646688692344</v>
       </c>
     </row>
     <row r="3">
@@ -26234,7 +26296,7 @@
         <v>5350</v>
       </c>
       <c r="G3" t="n">
-        <v>3.325029407347624</v>
+        <v>3.528327891210248</v>
       </c>
       <c r="H3" t="n">
         <v>4.415241698021699</v>
@@ -26243,13 +26305,13 @@
         <v>-6.801457550687495</v>
       </c>
       <c r="J3" t="n">
-        <v>6.17750577048104</v>
+        <v>6.386416680715135</v>
       </c>
       <c r="K3" t="n">
-        <v>1.999437867581366</v>
+        <v>2.200128166846271</v>
       </c>
       <c r="L3" t="n">
-        <v>1.996101198055822</v>
+        <v>2.071927334710266</v>
       </c>
       <c r="M3" t="n">
         <v>3.141373992581009</v>
@@ -26258,19 +26320,19 @@
         <v>-0.4217381452650604</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6915697205507665</v>
+        <v>-0.6177416573516781</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.867184537295751</v>
+        <v>-0.7934870299996621</v>
       </c>
       <c r="Q3" t="n">
         <v>3.028249761990343</v>
       </c>
       <c r="R3" t="n">
-        <v>1.915689786587027</v>
+        <v>2.134170982409711</v>
       </c>
       <c r="S3" t="n">
-        <v>36.00624017038956</v>
+        <v>35.80871051028911</v>
       </c>
     </row>
     <row r="4">
@@ -26301,7 +26363,7 @@
         <v>5350</v>
       </c>
       <c r="G4" t="n">
-        <v>1.448009110267034</v>
+        <v>1.549720060089022</v>
       </c>
       <c r="H4" t="n">
         <v>2.850971998464535</v>
@@ -26310,13 +26372,13 @@
         <v>-4.013658045530111</v>
       </c>
       <c r="J4" t="n">
-        <v>2.760376588863056</v>
+        <v>2.863403307658086</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6609396391598965</v>
+        <v>0.7618614795239065</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8615246119926923</v>
+        <v>0.9120407441869816</v>
       </c>
       <c r="M4" t="n">
         <v>1.530405410831581</v>
@@ -26325,19 +26387,19 @@
         <v>-0.03513590134540667</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6238818159373327</v>
+        <v>-0.5741096442152371</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3808410333468681</v>
+        <v>-0.3309471355220972</v>
       </c>
       <c r="Q4" t="n">
         <v>0.8890383481844566</v>
       </c>
       <c r="R4" t="n">
-        <v>1.758426926516221</v>
+        <v>2.035808012741236</v>
       </c>
       <c r="S4" t="n">
-        <v>34.64882194784262</v>
+        <v>34.48903141745727</v>
       </c>
     </row>
     <row r="5">
@@ -26368,7 +26430,7 @@
         <v>5350</v>
       </c>
       <c r="G5" t="n">
-        <v>1.322177495645649</v>
+        <v>1.441879364806353</v>
       </c>
       <c r="H5" t="n">
         <v>2.767005763541763</v>
@@ -26377,13 +26439,13 @@
         <v>-4.007835534325666</v>
       </c>
       <c r="J5" t="n">
-        <v>2.710543449184399</v>
+        <v>2.831885531808997</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5290334468223135</v>
+        <v>0.6477982967883822</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7907688311069805</v>
+        <v>0.8364100061531543</v>
       </c>
       <c r="M5" t="n">
         <v>1.482986017707999</v>
@@ -26392,19 +26454,19 @@
         <v>0.009155383054104682</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6911938151750285</v>
+        <v>-0.6462237186148356</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4568029468369761</v>
+        <v>-0.411726710847804</v>
       </c>
       <c r="Q5" t="n">
         <v>0.7663549252832969</v>
       </c>
       <c r="R5" t="n">
-        <v>1.741807877436763</v>
+        <v>2.054034418056427</v>
       </c>
       <c r="S5" t="n">
-        <v>34.51474392834017</v>
+        <v>34.3668978971317</v>
       </c>
     </row>
     <row r="6">
@@ -26435,7 +26497,7 @@
         <v>2081</v>
       </c>
       <c r="G6" t="n">
-        <v>3.802540398454268</v>
+        <v>4.000868417907788</v>
       </c>
       <c r="H6" t="n">
         <v>4.480839826499405</v>
@@ -26444,13 +26506,13 @@
         <v>-4.971559843100271</v>
       </c>
       <c r="J6" t="n">
-        <v>4.548480897974905</v>
+        <v>4.748234132084383</v>
       </c>
       <c r="K6" t="n">
-        <v>1.611802886879077</v>
+        <v>1.805945222339278</v>
       </c>
       <c r="L6" t="n">
-        <v>4.212177882370516</v>
+        <v>4.487893315345026</v>
       </c>
       <c r="M6" t="n">
         <v>4.170790846301431</v>
@@ -26459,19 +26521,19 @@
         <v>-0.6938477922258657</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7387032500493884</v>
+        <v>1.005228868727381</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1489142922244779</v>
+        <v>0.4138794990468098</v>
       </c>
       <c r="Q6" t="n">
         <v>2.610130415512946</v>
       </c>
       <c r="R6" t="n">
-        <v>1.801148831765809</v>
+        <v>2.128367392673436</v>
       </c>
       <c r="S6" t="n">
-        <v>36.53139195359947</v>
+        <v>36.58475252556579</v>
       </c>
     </row>
     <row r="7">
@@ -26502,7 +26564,7 @@
         <v>4759</v>
       </c>
       <c r="G7" t="n">
-        <v>1.023383277411472</v>
+        <v>1.025571908064027</v>
       </c>
       <c r="H7" t="n">
         <v>3.159499684461675</v>
@@ -26511,13 +26573,13 @@
         <v>-4.931510236495629</v>
       </c>
       <c r="J7" t="n">
-        <v>3.009217219425797</v>
+        <v>3.011448872365796</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4475354846956492</v>
+        <v>0.4497116398391565</v>
       </c>
       <c r="L7" t="n">
-        <v>1.422053332918938</v>
+        <v>1.49866381148307</v>
       </c>
       <c r="M7" t="n">
         <v>2.853371807541705</v>
@@ -26526,19 +26588,19 @@
         <v>-0.6519953497068132</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7444692035825207</v>
+        <v>-0.6694952362394146</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9985913415876291</v>
+        <v>-0.9238093287353921</v>
       </c>
       <c r="Q7" t="n">
         <v>1.029206964999307</v>
       </c>
       <c r="R7" t="n">
-        <v>1.572107476837847</v>
+        <v>1.9358185535582</v>
       </c>
       <c r="S7" t="n">
-        <v>34.66673865439584</v>
+        <v>34.48190722449114</v>
       </c>
     </row>
     <row r="8">
@@ -26569,7 +26631,7 @@
         <v>3879</v>
       </c>
       <c r="G8" t="n">
-        <v>1.377469513381224</v>
+        <v>1.417632263215163</v>
       </c>
       <c r="H8" t="n">
         <v>3.682979101677342</v>
@@ -26578,13 +26640,13 @@
         <v>-4.993938520359253</v>
       </c>
       <c r="J8" t="n">
-        <v>2.915944667371662</v>
+        <v>2.956716915480051</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2807541953956383</v>
+        <v>0.3204824591138022</v>
       </c>
       <c r="L8" t="n">
-        <v>1.777536904582333</v>
+        <v>1.89256014317134</v>
       </c>
       <c r="M8" t="n">
         <v>3.37529778912522</v>
@@ -26593,19 +26655,19 @@
         <v>-0.7172338472470785</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8343428761796834</v>
+        <v>-0.7222714369790606</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.162971507799715</v>
+        <v>-1.051271466165349</v>
       </c>
       <c r="Q8" t="n">
         <v>0.8116701183337849</v>
       </c>
       <c r="R8" t="n">
-        <v>1.619688553404086</v>
+        <v>1.97399327950627</v>
       </c>
       <c r="S8" t="n">
-        <v>34.59502691450788</v>
+        <v>34.44776363991227</v>
       </c>
     </row>
     <row r="9">
@@ -26636,7 +26698,7 @@
         <v>7479</v>
       </c>
       <c r="G9" t="n">
-        <v>1.235909519665546</v>
+        <v>1.234938041553724</v>
       </c>
       <c r="H9" t="n">
         <v>2.924673018099866</v>
@@ -26645,13 +26707,13 @@
         <v>-4.361298102541101</v>
       </c>
       <c r="J9" t="n">
-        <v>2.844582671861429</v>
+        <v>2.843595756630868</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5499777713367848</v>
+        <v>0.5490128755501811</v>
       </c>
       <c r="L9" t="n">
-        <v>1.635418270592304</v>
+        <v>1.709010384090659</v>
       </c>
       <c r="M9" t="n">
         <v>2.61924199400525</v>
@@ -26660,19 +26722,19 @@
         <v>-0.0561150756360651</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9031044194110271</v>
+        <v>-0.8313503979193393</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8976238998806507</v>
+        <v>-0.825865910057666</v>
       </c>
       <c r="Q9" t="n">
         <v>1.075852930172561</v>
       </c>
       <c r="R9" t="n">
-        <v>1.583193260796234</v>
+        <v>1.93263202983438</v>
       </c>
       <c r="S9" t="n">
-        <v>34.75718025845451</v>
+        <v>34.5579589382444</v>
       </c>
     </row>
     <row r="10">
@@ -26703,7 +26765,7 @@
         <v>6833</v>
       </c>
       <c r="G10" t="n">
-        <v>0.999147330817074</v>
+        <v>0.9733952059425066</v>
       </c>
       <c r="H10" t="n">
         <v>2.825804826151268</v>
@@ -26712,13 +26774,13 @@
         <v>-4.457012364616631</v>
       </c>
       <c r="J10" t="n">
-        <v>2.805600053601376</v>
+        <v>2.779387330817551</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4279130808196197</v>
+        <v>0.4023066056473068</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39772174365389</v>
+        <v>1.446242771469142</v>
       </c>
       <c r="M10" t="n">
         <v>2.520667195392101</v>
@@ -26727,19 +26789,19 @@
         <v>-0.1561379220853421</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9406664995013192</v>
+        <v>-0.893264441610031</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.017931244907488</v>
+        <v>-0.9705661598869764</v>
       </c>
       <c r="Q10" t="n">
         <v>0.9636248724831153</v>
       </c>
       <c r="R10" t="n">
-        <v>1.558813454328245</v>
+        <v>1.907619814890671</v>
       </c>
       <c r="S10" t="n">
-        <v>34.58065327040893</v>
+        <v>34.34851084457948</v>
       </c>
     </row>
     <row r="11">
@@ -26770,7 +26832,7 @@
         <v>4955</v>
       </c>
       <c r="G11" t="n">
-        <v>1.02830028824632</v>
+        <v>1.033696920439087</v>
       </c>
       <c r="H11" t="n">
         <v>3.052599744510709</v>
@@ -26779,13 +26841,13 @@
         <v>-5.33075675665221</v>
       </c>
       <c r="J11" t="n">
-        <v>3.555981335580127</v>
+        <v>3.561512988998383</v>
       </c>
       <c r="K11" t="n">
-        <v>0.59689868636712</v>
+        <v>0.6022722743656672</v>
       </c>
       <c r="L11" t="n">
-        <v>1.426989747825558</v>
+        <v>1.506826872418499</v>
       </c>
       <c r="M11" t="n">
         <v>2.746789095298907</v>
@@ -26794,19 +26856,19 @@
         <v>-1.06921398060964</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2176293339645308</v>
+        <v>-0.1390867529528106</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8513784976303063</v>
+        <v>-0.7733347652097766</v>
       </c>
       <c r="Q11" t="n">
         <v>1.333383038658331</v>
       </c>
       <c r="R11" t="n">
-        <v>1.611577587402224</v>
+        <v>1.939055194371875</v>
       </c>
       <c r="S11" t="n">
-        <v>34.81798370271414</v>
+        <v>34.63589748671272</v>
       </c>
     </row>
     <row r="12">
@@ -26837,7 +26899,7 @@
         <v>3613</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03049568832651506</v>
+        <v>0.05996017790037556</v>
       </c>
       <c r="H12" t="n">
         <v>3.020324205483638</v>
@@ -26846,13 +26908,13 @@
         <v>-5.518271219749737</v>
       </c>
       <c r="J12" t="n">
-        <v>2.768892762809183</v>
+        <v>2.799163861122644</v>
       </c>
       <c r="K12" t="n">
-        <v>0.07893751326615295</v>
+        <v>0.1084162716251003</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4252474970141584</v>
+        <v>0.5285302252907131</v>
       </c>
       <c r="M12" t="n">
         <v>2.714609334578899</v>
@@ -26861,19 +26923,19 @@
         <v>-1.26516942071554</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9760361657314531</v>
+        <v>-0.8741945929748862</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361882667990688</v>
+        <v>-1.260437920538959</v>
       </c>
       <c r="Q12" t="n">
         <v>0.563680258132937</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62358692521456</v>
+        <v>1.963635264809604</v>
       </c>
       <c r="S12" t="n">
-        <v>34.33219917528394</v>
+        <v>34.16163434943471</v>
       </c>
     </row>
     <row r="13">
@@ -26904,7 +26966,7 @@
         <v>5811</v>
       </c>
       <c r="G13" t="n">
-        <v>1.110274246265086</v>
+        <v>1.108585644429683</v>
       </c>
       <c r="H13" t="n">
         <v>2.894906402160435</v>
@@ -26913,13 +26975,13 @@
         <v>-5.374107922595961</v>
       </c>
       <c r="J13" t="n">
-        <v>3.846395090916221</v>
+        <v>3.844660794232158</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7668800872366655</v>
+        <v>0.7651972202883606</v>
       </c>
       <c r="L13" t="n">
-        <v>1.509287200874221</v>
+        <v>1.58206629226072</v>
       </c>
       <c r="M13" t="n">
         <v>2.589563711093512</v>
@@ -26928,19 +26990,19 @@
         <v>-1.114516602398308</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0622016580045015</v>
+        <v>0.1339432327866374</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6838442913343346</v>
+        <v>-0.6126376089529262</v>
       </c>
       <c r="Q13" t="n">
         <v>1.644784775979802</v>
       </c>
       <c r="R13" t="n">
-        <v>1.607314690852046</v>
+        <v>1.931907851171699</v>
       </c>
       <c r="S13" t="n">
-        <v>34.88879813968679</v>
+        <v>34.67510153127709</v>
       </c>
     </row>
     <row r="14">
@@ -26971,7 +27033,7 @@
         <v>2646</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.109804478654163</v>
+        <v>-0.06262472327238644</v>
       </c>
       <c r="H14" t="n">
         <v>3.050114968861273</v>
@@ -26980,13 +27042,13 @@
         <v>-6.369925976427937</v>
       </c>
       <c r="J14" t="n">
-        <v>3.528284062742082</v>
+        <v>3.577182146199442</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2683964266643413</v>
+        <v>0.3157548124522958</v>
       </c>
       <c r="L14" t="n">
-        <v>0.284393661431781</v>
+        <v>0.4053712721910019</v>
       </c>
       <c r="M14" t="n">
         <v>2.744311693270873</v>
@@ -26995,19 +27057,19 @@
         <v>-2.155161477362166</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2443173099666907</v>
+        <v>-0.1239775072229166</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.175151363745086</v>
+        <v>-1.055934468322495</v>
       </c>
       <c r="Q14" t="n">
         <v>1.017864047112793</v>
       </c>
       <c r="R14" t="n">
-        <v>1.675837361656218</v>
+        <v>1.981755096402904</v>
       </c>
       <c r="S14" t="n">
-        <v>34.52396900875332</v>
+        <v>34.38258932562495</v>
       </c>
     </row>
     <row r="15">
@@ -27038,7 +27100,7 @@
         <v>2768</v>
       </c>
       <c r="G15" t="n">
-        <v>3.793324617955718</v>
+        <v>3.93846854377784</v>
       </c>
       <c r="H15" t="n">
         <v>4.241141238419255</v>
@@ -27047,13 +27109,13 @@
         <v>-4.450865357859879</v>
       </c>
       <c r="J15" t="n">
-        <v>4.208587089822324</v>
+        <v>4.354311716047232</v>
       </c>
       <c r="K15" t="n">
-        <v>1.49667261239641</v>
+        <v>1.638604914642894</v>
       </c>
       <c r="L15" t="n">
-        <v>4.20292573350256</v>
+        <v>4.425201229306075</v>
       </c>
       <c r="M15" t="n">
         <v>3.931803568571701</v>
@@ -27062,19 +27124,19 @@
         <v>-0.1497142073784485</v>
       </c>
       <c r="O15" t="n">
-        <v>0.411195273061904</v>
+        <v>0.6253826200719459</v>
       </c>
       <c r="P15" t="n">
-        <v>0.03544152957266622</v>
+        <v>0.2488273554253295</v>
       </c>
       <c r="Q15" t="n">
         <v>2.601116658085023</v>
       </c>
       <c r="R15" t="n">
-        <v>1.716981472789292</v>
+        <v>2.076153516206181</v>
       </c>
       <c r="S15" t="n">
-        <v>36.29824293060733</v>
+        <v>36.29196116968658</v>
       </c>
     </row>
     <row r="16">
@@ -27105,7 +27167,7 @@
         <v>2582</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1609117116224468</v>
+        <v>-0.2232209609644209</v>
       </c>
       <c r="H16" t="n">
         <v>2.677332961555901</v>
@@ -27114,13 +27176,13 @@
         <v>-5.074785239078738</v>
       </c>
       <c r="J16" t="n">
-        <v>2.43407233368973</v>
+        <v>2.370143563269478</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01313707483378002</v>
+        <v>-0.07553854984455599</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2330847432422845</v>
+        <v>0.2440229795653837</v>
       </c>
       <c r="M16" t="n">
         <v>2.372635924022082</v>
@@ -27129,19 +27191,19 @@
         <v>-0.8017198868095488</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.298655639122304</v>
+        <v>-1.287884558567498</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.452631673225624</v>
+        <v>-1.441877395767854</v>
       </c>
       <c r="Q16" t="n">
         <v>0.2850684957467431</v>
       </c>
       <c r="R16" t="n">
-        <v>1.515925760162662</v>
+        <v>1.869993769571199</v>
       </c>
       <c r="S16" t="n">
-        <v>33.96705123420551</v>
+        <v>33.69917400901736</v>
       </c>
     </row>
     <row r="17">
@@ -27172,7 +27234,7 @@
         <v>5350</v>
       </c>
       <c r="G17" t="n">
-        <v>3.092291002968151</v>
+        <v>3.272599468906523</v>
       </c>
       <c r="H17" t="n">
         <v>4.098199081697951</v>
@@ -27181,13 +27243,13 @@
         <v>-5.966922000920871</v>
       </c>
       <c r="J17" t="n">
-        <v>5.317931954404842</v>
+        <v>5.502133067424619</v>
       </c>
       <c r="K17" t="n">
-        <v>1.652088731294898</v>
+        <v>1.829878282775987</v>
       </c>
       <c r="L17" t="n">
-        <v>1.814186025750697</v>
+        <v>1.935153254252242</v>
       </c>
       <c r="M17" t="n">
         <v>2.649453895119147</v>
@@ -27196,19 +27258,19 @@
         <v>-0.5797695896754385</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.23530365328851</v>
+        <v>-0.1167714595889935</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5893245831654847</v>
+        <v>-0.4712130079710386</v>
       </c>
       <c r="Q17" t="n">
         <v>3.668783108241125</v>
       </c>
       <c r="R17" t="n">
-        <v>1.771832064412715</v>
+        <v>2.111892135877413</v>
       </c>
       <c r="S17" t="n">
-        <v>36.23473689174994</v>
+        <v>36.26827429609483</v>
       </c>
     </row>
     <row r="18">
@@ -27239,7 +27301,7 @@
         <v>5350</v>
       </c>
       <c r="G18" t="n">
-        <v>3.516123814346561</v>
+        <v>3.654325547407811</v>
       </c>
       <c r="H18" t="n">
         <v>5.783756108550131</v>
@@ -27248,13 +27310,13 @@
         <v>-8.135060086053226</v>
       </c>
       <c r="J18" t="n">
-        <v>6.521978047361277</v>
+        <v>6.664192819638282</v>
       </c>
       <c r="K18" t="n">
-        <v>1.256607060998194</v>
+        <v>1.391792170951001</v>
       </c>
       <c r="L18" t="n">
-        <v>1.902519375385214</v>
+        <v>2.002449799272044</v>
       </c>
       <c r="M18" t="n">
         <v>3.199911187023963</v>
@@ -27263,19 +27325,19 @@
         <v>-0.866778170699134</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3937988821282268</v>
+        <v>-0.2961203363918363</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9006953731968803</v>
+        <v>-0.8035139141029712</v>
       </c>
       <c r="Q18" t="n">
         <v>4.279024529710918</v>
       </c>
       <c r="R18" t="n">
-        <v>1.70548293970374</v>
+        <v>2.069699162765271</v>
       </c>
       <c r="S18" t="n">
-        <v>35.87193621141898</v>
+        <v>35.76965964884482</v>
       </c>
     </row>
     <row r="19">
@@ -27306,7 +27368,7 @@
         <v>5350</v>
       </c>
       <c r="G19" t="n">
-        <v>3.107297827612987</v>
+        <v>3.199778408234222</v>
       </c>
       <c r="H19" t="n">
         <v>5.165126385122076</v>
@@ -27315,13 +27377,13 @@
         <v>-7.767586524326864</v>
       </c>
       <c r="J19" t="n">
-        <v>6.30020059860088</v>
+        <v>6.395545006597581</v>
       </c>
       <c r="K19" t="n">
-        <v>1.249951167098917</v>
+        <v>1.340765827836687</v>
       </c>
       <c r="L19" t="n">
-        <v>1.616196592624308</v>
+        <v>1.700215724633947</v>
       </c>
       <c r="M19" t="n">
         <v>3.045753641844939</v>
@@ -27330,19 +27392,19 @@
         <v>-0.3954191213578206</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9958217594373986</v>
+        <v>-0.9139623177339629</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.159802603311677</v>
+        <v>-1.078078745586308</v>
       </c>
       <c r="Q19" t="n">
         <v>6.152759588847778</v>
       </c>
       <c r="R19" t="n">
-        <v>1.623759248380208</v>
+        <v>1.952145156434337</v>
       </c>
       <c r="S19" t="n">
-        <v>34.70719153972348</v>
+        <v>34.44091268327063</v>
       </c>
     </row>
     <row r="20">
@@ -27373,7 +27435,7 @@
         <v>5350</v>
       </c>
       <c r="G20" t="n">
-        <v>1.194146566124044</v>
+        <v>1.201300550931395</v>
       </c>
       <c r="H20" t="n">
         <v>3.196375734217916</v>
@@ -27382,13 +27444,13 @@
         <v>-4.722140616290904</v>
       </c>
       <c r="J20" t="n">
-        <v>2.919805244903695</v>
+        <v>2.927081226253225</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4756016834724264</v>
+        <v>0.4827048702904735</v>
       </c>
       <c r="L20" t="n">
-        <v>1.601974193925093</v>
+        <v>1.686563976729616</v>
       </c>
       <c r="M20" t="n">
         <v>2.884978590088161</v>
@@ -27397,19 +27459,19 @@
         <v>-0.5940767297745286</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6568533913770658</v>
+        <v>-0.5741442190267287</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8887943438002477</v>
+        <v>-0.8062782763077814</v>
       </c>
       <c r="Q20" t="n">
         <v>0.9716313378422159</v>
       </c>
       <c r="R20" t="n">
-        <v>1.582116498445374</v>
+        <v>1.940816464869588</v>
       </c>
       <c r="S20" t="n">
-        <v>34.74197206753804</v>
+        <v>34.56459730278181</v>
       </c>
     </row>
     <row r="21">
@@ -27440,7 +27502,7 @@
         <v>5350</v>
       </c>
       <c r="G21" t="n">
-        <v>1.203376168781634</v>
+        <v>1.212642270288233</v>
       </c>
       <c r="H21" t="n">
         <v>3.216877010413599</v>
@@ -27449,13 +27511,13 @@
         <v>-4.857384674978816</v>
       </c>
       <c r="J21" t="n">
-        <v>3.055031625224136</v>
+        <v>3.064467262847659</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5159451667158033</v>
+        <v>0.5251483275806601</v>
       </c>
       <c r="L21" t="n">
-        <v>1.918857014651776</v>
+        <v>2.019577286550822</v>
       </c>
       <c r="M21" t="n">
         <v>3.49348069987867</v>
@@ -27464,19 +27526,19 @@
         <v>-0.6888022412894546</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8384443585846779</v>
+        <v>-0.7404489616710586</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.114814019154031</v>
+        <v>-1.017091741741272</v>
       </c>
       <c r="Q21" t="n">
         <v>1.096065848739647</v>
       </c>
       <c r="R21" t="n">
-        <v>1.586978170777953</v>
+        <v>1.942943164368582</v>
       </c>
       <c r="S21" t="n">
-        <v>34.78276900944921</v>
+        <v>34.60646688692344</v>
       </c>
     </row>
   </sheetData>
@@ -27532,10 +27594,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.203376168781634</v>
+        <v>1.212642270288233</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1609117116224468</v>
+        <v>-0.2232209609644209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -27543,7 +27605,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.802540398454268</v>
+        <v>4.000868417907788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -27619,10 +27681,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.055031625224136</v>
+        <v>3.064467262847659</v>
       </c>
       <c r="C5" t="n">
-        <v>2.43407233368973</v>
+        <v>2.370143563269478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -27630,7 +27692,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6.521978047361277</v>
+        <v>6.664192819638282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -27648,10 +27710,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5159451667158033</v>
+        <v>0.5251483275806601</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.01313707483378002</v>
+        <v>-0.07553854984455599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -27659,7 +27721,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.999437867581366</v>
+        <v>2.200128166846271</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27677,10 +27739,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.602756532869787</v>
+        <v>1.68661020412284</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2330847432422845</v>
+        <v>0.2440229795653837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -27688,7 +27750,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.212177882370516</v>
+        <v>4.487893315345026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -27764,10 +27826,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7003242883177885</v>
+        <v>-0.6183713704363991</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.298655639122304</v>
+        <v>-1.287884558567498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -27775,7 +27837,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7387032500493884</v>
+        <v>1.005228868727381</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -27793,10 +27855,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.9311665426297688</v>
+        <v>-0.8494041409426778</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.452631673225624</v>
+        <v>-1.441877395767854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -27804,7 +27866,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.1489142922244779</v>
+        <v>0.4138794990468098</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -27855,7 +27917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U118"/>
+  <dimension ref="A1:U119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35802,6 +35864,73 @@
       </c>
       <c r="U118" t="n">
         <v>12424.50167634108</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12665.90268236841</v>
+      </c>
+      <c r="C119" t="n">
+        <v>12955.69107302451</v>
+      </c>
+      <c r="D119" t="n">
+        <v>12708.08510529739</v>
+      </c>
+      <c r="E119" t="n">
+        <v>12694.58975806595</v>
+      </c>
+      <c r="F119" t="n">
+        <v>13014.82550712655</v>
+      </c>
+      <c r="G119" t="n">
+        <v>12642.49241513757</v>
+      </c>
+      <c r="H119" t="n">
+        <v>12691.5554392082</v>
+      </c>
+      <c r="I119" t="n">
+        <v>12668.6928088066</v>
+      </c>
+      <c r="J119" t="n">
+        <v>12635.96294395161</v>
+      </c>
+      <c r="K119" t="n">
+        <v>12643.5091914387</v>
+      </c>
+      <c r="L119" t="n">
+        <v>12521.6543070824</v>
+      </c>
+      <c r="M119" t="n">
+        <v>12652.88087929108</v>
+      </c>
+      <c r="N119" t="n">
+        <v>12506.31384769161</v>
+      </c>
+      <c r="O119" t="n">
+        <v>13007.01669277892</v>
+      </c>
+      <c r="P119" t="n">
+        <v>12486.2165923277</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>12923.68883261896</v>
+      </c>
+      <c r="R119" t="n">
+        <v>12971.45860972554</v>
+      </c>
+      <c r="S119" t="n">
+        <v>12557.38330442766</v>
+      </c>
+      <c r="T119" t="n">
+        <v>12664.48336250478</v>
+      </c>
+      <c r="U119" t="n">
+        <v>12665.90268236841</v>
       </c>
     </row>
   </sheetData>
@@ -35879,22 +36008,22 @@
         <v>28.7899256857766</v>
       </c>
       <c r="E2" t="n">
-        <v>3.957029030483383</v>
+        <v>4.15535856360334</v>
       </c>
       <c r="F2" t="n">
-        <v>2.720910078246175</v>
+        <v>2.907459213896013</v>
       </c>
       <c r="G2" t="n">
-        <v>4.509434913695443</v>
+        <v>4.708818328423336</v>
       </c>
       <c r="H2" t="n">
-        <v>1.411287993933641</v>
+        <v>1.595458754356183</v>
       </c>
       <c r="I2" t="n">
-        <v>1.508838818296399</v>
+        <v>1.702497686755211</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9877971598772683</v>
+        <v>1.171198828116071</v>
       </c>
     </row>
     <row r="3">
@@ -35911,22 +36040,22 @@
         <v>35.23600097747185</v>
       </c>
       <c r="E3" t="n">
-        <v>4.010285297203331</v>
+        <v>4.215104428620498</v>
       </c>
       <c r="F3" t="n">
-        <v>2.773533092157399</v>
+        <v>2.966489255674376</v>
       </c>
       <c r="G3" t="n">
-        <v>4.554244984781719</v>
+        <v>4.760135292481293</v>
       </c>
       <c r="H3" t="n">
-        <v>1.454769685588686</v>
+        <v>1.645249885500433</v>
       </c>
       <c r="I3" t="n">
-        <v>1.590345761867473</v>
+        <v>1.790399500013251</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06888573088546</v>
+        <v>1.258641437970875</v>
       </c>
     </row>
     <row r="4">
@@ -35943,22 +36072,22 @@
         <v>39.58466910448775</v>
       </c>
       <c r="E4" t="n">
-        <v>3.802540398454268</v>
+        <v>4.000868417907788</v>
       </c>
       <c r="F4" t="n">
-        <v>2.568258419894898</v>
+        <v>2.75482003539993</v>
       </c>
       <c r="G4" t="n">
-        <v>4.548480897974905</v>
+        <v>4.748234132084383</v>
       </c>
       <c r="H4" t="n">
-        <v>1.449176473189517</v>
+        <v>1.633702588247576</v>
       </c>
       <c r="I4" t="n">
-        <v>1.611802886879077</v>
+        <v>1.805945222339278</v>
       </c>
       <c r="J4" t="n">
-        <v>1.090232717153183</v>
+        <v>1.27410594867754</v>
       </c>
     </row>
     <row r="5">
@@ -35975,22 +36104,22 @@
         <v>46.52965386613435</v>
       </c>
       <c r="E5" t="n">
-        <v>3.695962923552454</v>
+        <v>3.890347351189338</v>
       </c>
       <c r="F5" t="n">
-        <v>2.462948222808126</v>
+        <v>2.645623136436148</v>
       </c>
       <c r="G5" t="n">
-        <v>4.377201032192479</v>
+        <v>4.572862482348827</v>
       </c>
       <c r="H5" t="n">
-        <v>1.282974141210902</v>
+        <v>1.463545351332662</v>
       </c>
       <c r="I5" t="n">
-        <v>1.559336046707083</v>
+        <v>1.749715236523497</v>
       </c>
       <c r="J5" t="n">
-        <v>1.038035187611985</v>
+        <v>1.218169711078043</v>
       </c>
     </row>
     <row r="6">
@@ -36007,22 +36136,22 @@
         <v>53.08314290320629</v>
       </c>
       <c r="E6" t="n">
-        <v>3.509798852842394</v>
+        <v>3.693802310147554</v>
       </c>
       <c r="F6" t="n">
-        <v>2.278997768033197</v>
+        <v>2.45143292794725</v>
       </c>
       <c r="G6" t="n">
-        <v>4.517770583752401</v>
+        <v>4.703565854831804</v>
       </c>
       <c r="H6" t="n">
-        <v>1.41937655586557</v>
+        <v>1.590362455184402</v>
       </c>
       <c r="I6" t="n">
-        <v>1.566207176346346</v>
+        <v>1.746755621739293</v>
       </c>
       <c r="J6" t="n">
-        <v>1.044871047960183</v>
+        <v>1.21522555746727</v>
       </c>
     </row>
     <row r="7">
@@ -36039,22 +36168,22 @@
         <v>67.27673032288681</v>
       </c>
       <c r="E7" t="n">
-        <v>3.053494116665889</v>
+        <v>3.206265349618254</v>
       </c>
       <c r="F7" t="n">
-        <v>1.828118801885359</v>
+        <v>1.969737213268319</v>
       </c>
       <c r="G7" t="n">
-        <v>4.052078859447672</v>
+        <v>4.206330440287998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9674901055287233</v>
+        <v>1.107911589479449</v>
       </c>
       <c r="I7" t="n">
-        <v>1.297088078234943</v>
+        <v>1.447255534203751</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7771333296658023</v>
+        <v>0.9172900731449163</v>
       </c>
     </row>
   </sheetData>
@@ -36170,11 +36299,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>haber_minimo</t>
@@ -40886,12 +41010,24 @@
       <c r="L119" t="n">
         <v>198366.6517470242</v>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>96455.44748777211</v>
+      </c>
+      <c r="N119" t="n">
+        <v>112207.5667606196</v>
+      </c>
+      <c r="O119" t="n">
+        <v>93587.48950962856</v>
+      </c>
+      <c r="P119" t="n">
+        <v>108871.2431554651</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>92083.12511134527</v>
+      </c>
+      <c r="R119" t="n">
+        <v>107121.2013169876</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -42570,7 +42706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44813,6 +44949,25 @@
       </c>
       <c r="E118" t="n">
         <v>1.801148831765809</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1.933610203208236</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.858878113665119</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.942943164368582</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.128367392673436</v>
       </c>
     </row>
   </sheetData>
@@ -44826,7 +44981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48857,6 +49012,40 @@
       </c>
       <c r="J118" t="n">
         <v>0.009410829867206871</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12514.1508</v>
+      </c>
+      <c r="C119" t="n">
+        <v>12511.50846558987</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-0.02111477200774647</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-0.01276120238633549</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.04360856387767287</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.04729765295756749</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-0.05890471522876917</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-0.01478170675885959</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.01879534643134395</v>
       </c>
     </row>
   </sheetData>
@@ -58065,7 +58254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV118"/>
+  <dimension ref="A1:AV119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75624,6 +75813,154 @@
       </c>
       <c r="AV118" t="n">
         <v>10754.98355833332</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12291.30673037975</v>
+      </c>
+      <c r="C119" t="n">
+        <v>14594.13773932586</v>
+      </c>
+      <c r="D119" t="n">
+        <v>6214.25405</v>
+      </c>
+      <c r="E119" t="n">
+        <v>9369.250045977013</v>
+      </c>
+      <c r="F119" t="n">
+        <v>10699.26531257485</v>
+      </c>
+      <c r="G119" t="n">
+        <v>13887.67354461538</v>
+      </c>
+      <c r="H119" t="n">
+        <v>10420.32237405063</v>
+      </c>
+      <c r="I119" t="n">
+        <v>9217.253022641518</v>
+      </c>
+      <c r="J119" t="n">
+        <v>12543.19654520548</v>
+      </c>
+      <c r="K119" t="n">
+        <v>12851.04233333338</v>
+      </c>
+      <c r="L119" t="n">
+        <v>11345.10385786518</v>
+      </c>
+      <c r="M119" t="n">
+        <v>5986.460253124989</v>
+      </c>
+      <c r="N119" t="n">
+        <v>9221.861046640317</v>
+      </c>
+      <c r="O119" t="n">
+        <v>12661.68072981367</v>
+      </c>
+      <c r="P119" t="n">
+        <v>11832.04455894737</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>10227.41730207613</v>
+      </c>
+      <c r="R119" t="n">
+        <v>9202.745592307669</v>
+      </c>
+      <c r="S119" t="n">
+        <v>7660.370441176466</v>
+      </c>
+      <c r="T119" t="n">
+        <v>12311.19307361101</v>
+      </c>
+      <c r="U119" t="n">
+        <v>12776.29811304348</v>
+      </c>
+      <c r="V119" t="n">
+        <v>8553.057274074077</v>
+      </c>
+      <c r="W119" t="n">
+        <v>12413.76181592357</v>
+      </c>
+      <c r="X119" t="n">
+        <v>11815.21279411766</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>9067.766757619047</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>10571.27030909093</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>11884.43326190474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>14746.25172288556</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>8246.246924586285</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>12858.20628474576</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>11855.45096769231</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>8935.929343127966</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>8615.766052173933</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>11750.74883703699</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>11605.17143181819</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>9390.285220000003</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>13038.81504929577</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>11339.25117165354</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>9711.480533333337</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>9402.407169696973</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>12521.51365769231</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>11840.92426526321</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>17566.48882786071</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>9911.53622528409</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>12970.14126533334</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>12863.78882842105</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>9883.822665753423</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>10965.50699583334</v>
       </c>
     </row>
   </sheetData>
@@ -75695,10 +76032,10 @@
         <v>0.00789999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>12239.89082531654</v>
+        <v>12291.30673037975</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3690302824563861</v>
+        <v>0.5069943760275871</v>
       </c>
     </row>
     <row r="3">
@@ -75724,10 +76061,10 @@
         <v>0.008899999999999991</v>
       </c>
       <c r="F3" t="n">
-        <v>14256.30229550564</v>
+        <v>14594.13773932586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4837335365578086</v>
+        <v>0.4889205933624573</v>
       </c>
     </row>
     <row r="4">
@@ -75753,10 +76090,10 @@
         <v>0.02320000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>6016.592250000002</v>
+        <v>6214.25405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4724296880092073</v>
+        <v>0.4595841821558853</v>
       </c>
     </row>
     <row r="5">
@@ -75782,10 +76119,10 @@
         <v>0.02610000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>9271.639020689654</v>
+        <v>9369.250045977013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04132120632541578</v>
+        <v>0.04612171191946733</v>
       </c>
     </row>
     <row r="6">
@@ -75811,10 +76148,10 @@
         <v>0.01669999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>10396.32454610778</v>
+        <v>10699.26531257485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3185941112143214</v>
+        <v>0.3114508173920104</v>
       </c>
     </row>
     <row r="7">
@@ -75840,10 +76177,10 @@
         <v>0.013</v>
       </c>
       <c r="F7" t="n">
-        <v>13759.20745538462</v>
+        <v>13887.67354461538</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1666791034235643</v>
+        <v>0.1673606996405043</v>
       </c>
     </row>
     <row r="8">
@@ -75869,10 +76206,10 @@
         <v>0.0158</v>
       </c>
       <c r="F8" t="n">
-        <v>10758.8303449367</v>
+        <v>10420.32237405063</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2254536911485026</v>
+        <v>0.2634623694340384</v>
       </c>
     </row>
     <row r="9">
@@ -75898,10 +76235,10 @@
         <v>0.005299999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>10136.66003207545</v>
+        <v>9217.253022641518</v>
       </c>
       <c r="G9" t="n">
-        <v>1.269592525906271</v>
+        <v>1.711918338472199</v>
       </c>
     </row>
     <row r="10">
@@ -75927,10 +76264,10 @@
         <v>0.007299999999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>12480.93234794521</v>
+        <v>12543.19654520548</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03581550929427328</v>
+        <v>0.006111928759163892</v>
       </c>
     </row>
     <row r="11">
@@ -75956,10 +76293,10 @@
         <v>0.008399999999999963</v>
       </c>
       <c r="F11" t="n">
-        <v>12538.16430357141</v>
+        <v>12851.04233333338</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2483693277166805</v>
+        <v>0.2658810930431499</v>
       </c>
     </row>
     <row r="12">
@@ -75985,10 +76322,10 @@
         <v>0.0178</v>
       </c>
       <c r="F12" t="n">
-        <v>11054.76521179775</v>
+        <v>11345.10385786518</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2770253577883587</v>
+        <v>0.2938099655627578</v>
       </c>
     </row>
     <row r="13">
@@ -76014,10 +76351,10 @@
         <v>0.003200000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5788.478687500011</v>
+        <v>5986.460253124989</v>
       </c>
       <c r="G13" t="n">
-        <v>4.050894725185516</v>
+        <v>4.04142310921798</v>
       </c>
     </row>
     <row r="14">
@@ -76043,10 +76380,10 @@
         <v>0.0253</v>
       </c>
       <c r="F14" t="n">
-        <v>9094.007722924902</v>
+        <v>9221.861046640317</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0608401535580978</v>
+        <v>0.06329580479325635</v>
       </c>
     </row>
     <row r="15">
@@ -76072,10 +76409,10 @@
         <v>0.0161</v>
       </c>
       <c r="F15" t="n">
-        <v>12301.79348509317</v>
+        <v>12661.68072981367</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1998423921589769</v>
+        <v>0.1915007361300299</v>
       </c>
     </row>
     <row r="16">
@@ -76101,10 +76438,10 @@
         <v>0.009499999999999995</v>
       </c>
       <c r="F16" t="n">
-        <v>11579.24136210526</v>
+        <v>11832.04455894737</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01985339172080222</v>
+        <v>0.002624459038841164</v>
       </c>
     </row>
     <row r="17">
@@ -76130,10 +76467,10 @@
         <v>0.0289</v>
       </c>
       <c r="F17" t="n">
-        <v>10456.429183391</v>
+        <v>10227.41730207613</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07877957452700132</v>
+        <v>0.1101389907557626</v>
       </c>
     </row>
     <row r="18">
@@ -76159,10 +76496,10 @@
         <v>0.002600000000000005</v>
       </c>
       <c r="F18" t="n">
-        <v>10124.42154615391</v>
+        <v>9202.745592307669</v>
       </c>
       <c r="G18" t="n">
-        <v>2.630010179109404</v>
+        <v>3.483402600737438</v>
       </c>
     </row>
     <row r="19">
@@ -76188,10 +76525,10 @@
         <v>0.005099999999999997</v>
       </c>
       <c r="F19" t="n">
-        <v>7450.345496078427</v>
+        <v>7660.370441176466</v>
       </c>
       <c r="G19" t="n">
-        <v>1.692627089800205</v>
+        <v>1.648095931420173</v>
       </c>
     </row>
     <row r="20">
@@ -76217,10 +76554,10 @@
         <v>0.007199999999999984</v>
       </c>
       <c r="F20" t="n">
-        <v>12017.20407499998</v>
+        <v>12311.19307361101</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6425058264858851</v>
+        <v>0.6301479475866127</v>
       </c>
     </row>
     <row r="21">
@@ -76246,10 +76583,10 @@
         <v>0.01380000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>12656.42364492754</v>
+        <v>12776.29811304348</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7928464652632883</v>
+        <v>0.824806285876138</v>
       </c>
     </row>
     <row r="22">
@@ -76275,10 +76612,10 @@
         <v>0.0243</v>
       </c>
       <c r="F22" t="n">
-        <v>8529.42889259259</v>
+        <v>8553.057274074077</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09266351368229581</v>
+        <v>0.1062803345275335</v>
       </c>
     </row>
     <row r="23">
@@ -76304,10 +76641,10 @@
         <v>0.0157</v>
       </c>
       <c r="F23" t="n">
-        <v>11931.68806560509</v>
+        <v>12413.76181592357</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2490103251747015</v>
+        <v>0.244297089184885</v>
       </c>
     </row>
     <row r="24">
@@ -76333,10 +76670,10 @@
         <v>0.0068</v>
       </c>
       <c r="F24" t="n">
-        <v>11511.60655882353</v>
+        <v>11815.21279411766</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05396411780539625</v>
+        <v>0.01588399058811804</v>
       </c>
     </row>
     <row r="25">
@@ -76362,10 +76699,10 @@
         <v>0.02099999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>8952.829288095238</v>
+        <v>9067.766757619047</v>
       </c>
       <c r="G25" t="n">
-        <v>0.202325279089991</v>
+        <v>0.2208815778518824</v>
       </c>
     </row>
     <row r="26">
@@ -76391,10 +76728,10 @@
         <v>0.002200000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>10400.39517272726</v>
+        <v>10571.27030909093</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5664578115205778</v>
+        <v>0.6077722814823782</v>
       </c>
     </row>
     <row r="27">
@@ -76420,10 +76757,10 @@
         <v>0.006299999999999972</v>
       </c>
       <c r="F27" t="n">
-        <v>11223.33246984127</v>
+        <v>11884.43326190474</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9105731410154854</v>
+        <v>0.7714085966524297</v>
       </c>
     </row>
     <row r="28">
@@ -76449,10 +76786,10 @@
         <v>0.02010000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>14423.45511791046</v>
+        <v>14746.25172288556</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4996468019635715</v>
+        <v>0.5271199370703984</v>
       </c>
     </row>
     <row r="29">
@@ -76478,10 +76815,10 @@
         <v>0.0423</v>
       </c>
       <c r="F29" t="n">
-        <v>8126.956556973996</v>
+        <v>8246.246924586285</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06799306389457131</v>
+        <v>0.06899121161301676</v>
       </c>
     </row>
     <row r="30">
@@ -76507,10 +76844,10 @@
         <v>0.0118</v>
       </c>
       <c r="F30" t="n">
-        <v>12651.1503881356</v>
+        <v>12858.20628474576</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2540369540446852</v>
+        <v>0.2580671784255947</v>
       </c>
     </row>
     <row r="31">
@@ -76536,10 +76873,10 @@
         <v>0.006499999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>11574.43192923076</v>
+        <v>11855.45096769231</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08911263347989155</v>
+        <v>0.05809271870759387</v>
       </c>
     </row>
     <row r="32">
@@ -76565,10 +76902,10 @@
         <v>0.0211</v>
       </c>
       <c r="F32" t="n">
-        <v>8879.584163981044</v>
+        <v>8935.929343127966</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2434400740388848</v>
+        <v>0.2501654440957456</v>
       </c>
     </row>
     <row r="33">
@@ -76594,10 +76931,10 @@
         <v>0.0023</v>
       </c>
       <c r="F33" t="n">
-        <v>8514.163778260869</v>
+        <v>8615.766052173933</v>
       </c>
       <c r="G33" t="n">
-        <v>2.297401001697756</v>
+        <v>2.380993188681336</v>
       </c>
     </row>
     <row r="34">
@@ -76623,10 +76960,10 @@
         <v>0.008099999999999996</v>
       </c>
       <c r="F34" t="n">
-        <v>11592.72773580249</v>
+        <v>11750.74883703699</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5938106422164654</v>
+        <v>0.6882287742807349</v>
       </c>
     </row>
     <row r="35">
@@ -76652,10 +76989,10 @@
         <v>0.0176</v>
       </c>
       <c r="F35" t="n">
-        <v>11376.57394772728</v>
+        <v>11605.17143181819</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5191339318381083</v>
+        <v>0.5289516708496298</v>
       </c>
     </row>
     <row r="36">
@@ -76681,10 +77018,10 @@
         <v>0.026</v>
       </c>
       <c r="F36" t="n">
-        <v>9312.925318461539</v>
+        <v>9390.285220000003</v>
       </c>
       <c r="G36" t="n">
-        <v>0.03502361686057725</v>
+        <v>0.03986869608592884</v>
       </c>
     </row>
     <row r="37">
@@ -76710,10 +77047,10 @@
         <v>0.0142</v>
       </c>
       <c r="F37" t="n">
-        <v>12683.48952957746</v>
+        <v>13038.81504929577</v>
       </c>
       <c r="G37" t="n">
-        <v>0.169704023559376</v>
+        <v>0.1654898813008554</v>
       </c>
     </row>
     <row r="38">
@@ -76739,10 +77076,10 @@
         <v>0.0127</v>
       </c>
       <c r="F38" t="n">
-        <v>11049.75512047244</v>
+        <v>11339.25117165354</v>
       </c>
       <c r="G38" t="n">
-        <v>0.03547877677533433</v>
+        <v>0.01881010122556974</v>
       </c>
     </row>
     <row r="39">
@@ -76768,10 +77105,10 @@
         <v>0.02519999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>9790.18401904762</v>
+        <v>9711.480533333337</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1325449256415415</v>
+        <v>0.1532974122422152</v>
       </c>
     </row>
     <row r="40">
@@ -76797,10 +77134,10 @@
         <v>0.003300000000000011</v>
       </c>
       <c r="F40" t="n">
-        <v>10290.63012121217</v>
+        <v>9402.407169696973</v>
       </c>
       <c r="G40" t="n">
-        <v>2.165787394389641</v>
+        <v>2.846528072410748</v>
       </c>
     </row>
     <row r="41">
@@ -76826,10 +77163,10 @@
         <v>0.0052</v>
       </c>
       <c r="F41" t="n">
-        <v>12396.47101346154</v>
+        <v>12521.51365769231</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0885409367631894</v>
+        <v>0.08615369866303953</v>
       </c>
     </row>
     <row r="42">
@@ -76855,10 +77192,10 @@
         <v>0.009500000000000008</v>
       </c>
       <c r="F42" t="n">
-        <v>11684.62373684206</v>
+        <v>11840.92426526321</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2872459477834413</v>
+        <v>0.2881961787568247</v>
       </c>
     </row>
     <row r="43">
@@ -76884,10 +77221,10 @@
         <v>0.02009999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>17421.93214577114</v>
+        <v>17566.48882786071</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3311375502495481</v>
+        <v>0.3371108705494911</v>
       </c>
     </row>
     <row r="44">
@@ -76913,10 +77250,10 @@
         <v>0.0352</v>
       </c>
       <c r="F44" t="n">
-        <v>9932.991592613636</v>
+        <v>9911.53622528409</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01670315476243592</v>
+        <v>0.02271564973017861</v>
       </c>
     </row>
     <row r="45">
@@ -76942,10 +77279,10 @@
         <v>0.015</v>
       </c>
       <c r="F45" t="n">
-        <v>12637.59807733334</v>
+        <v>12970.14126533334</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1858146732318263</v>
+        <v>0.1778327255427299</v>
       </c>
     </row>
     <row r="46">
@@ -76971,10 +77308,10 @@
         <v>0.009499999999999995</v>
       </c>
       <c r="F46" t="n">
-        <v>12631.59945263158</v>
+        <v>12863.78882842105</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1880253852000667</v>
+        <v>0.1683935564772137</v>
       </c>
     </row>
     <row r="47">
@@ -77000,10 +77337,10 @@
         <v>0.0292</v>
       </c>
       <c r="F47" t="n">
-        <v>9742.336124657531</v>
+        <v>9883.822665753423</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1121323489457941</v>
+        <v>0.1116386353492739</v>
       </c>
     </row>
     <row r="48">
@@ -77029,10 +77366,10 @@
         <v>0.004799999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>10754.98355833332</v>
+        <v>10965.50699583334</v>
       </c>
       <c r="G48" t="n">
-        <v>0.46826123492695</v>
+        <v>0.4421071479055657</v>
       </c>
     </row>
   </sheetData>
@@ -77840,23 +78177,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12176.766</v>
+        <v>12414.1508</v>
       </c>
       <c r="F2" t="n">
-        <v>12346.56240027759</v>
+        <v>12599.31770285615</v>
       </c>
       <c r="G2" t="n">
-        <v>1.383071081403653</v>
+        <v>1.47966015285792</v>
       </c>
       <c r="H2" t="n">
-        <v>12571.37847475568</v>
+        <v>12829.9575931697</v>
       </c>
       <c r="I2" t="n">
-        <v>3.214303137778152</v>
+        <v>3.322692844405428</v>
       </c>
     </row>
     <row r="3">
@@ -77945,23 +78282,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>335.9549794131011</v>
+        <v>344.3846493764272</v>
       </c>
       <c r="F5" t="n">
-        <v>348.654501902532</v>
+        <v>357.7654355671619</v>
       </c>
       <c r="G5" t="n">
-        <v>2.913035310785417</v>
+        <v>3.011082000584642</v>
       </c>
       <c r="H5" t="n">
-        <v>364.6743527602758</v>
+        <v>374.1567531735959</v>
       </c>
       <c r="I5" t="n">
-        <v>6.58769246903379</v>
+        <v>6.699624714522834</v>
       </c>
     </row>
     <row r="6">
@@ -78015,23 +78352,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59.56269863266965</v>
+        <v>62.64801925394536</v>
       </c>
       <c r="F7" t="n">
-        <v>60.57187979230802</v>
+        <v>63.83265114083771</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6324668411140433</v>
+        <v>0.7283408013981196</v>
       </c>
       <c r="H7" t="n">
-        <v>60.68095629974959</v>
+        <v>63.95990026852822</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7008264943263898</v>
+        <v>0.8065766927874973</v>
       </c>
     </row>
     <row r="8">
@@ -78156,32 +78493,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7766117799357913</v>
+        <v>0.7782823708693432</v>
       </c>
       <c r="F2" t="n">
-        <v>1.61860992650482</v>
+        <v>1.646885450463722</v>
       </c>
       <c r="G2" t="n">
-        <v>1.238105220689949</v>
+        <v>1.295464858529232</v>
       </c>
       <c r="H2" t="n">
-        <v>2.000493659661787</v>
+        <v>2.097240340882497</v>
       </c>
       <c r="I2" t="n">
-        <v>3.165817238816628</v>
+        <v>3.350225344644017</v>
       </c>
       <c r="J2" t="n">
-        <v>4.468613961766402</v>
+        <v>4.67646682302717</v>
       </c>
       <c r="K2" t="n">
-        <v>1.986582682653389</v>
+        <v>2.14464976258323</v>
       </c>
       <c r="L2" t="n">
-        <v>3.188424725460727</v>
+        <v>3.382555186403092</v>
       </c>
     </row>
     <row r="3">
@@ -78288,32 +78625,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.454621090147767</v>
+        <v>2.445254200077319</v>
       </c>
       <c r="F5" t="n">
-        <v>3.560977464015705</v>
+        <v>3.591015537868183</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.182506561138812</v>
+        <v>-1.109283683161021</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2047723712314464</v>
+        <v>-0.1268724483923589</v>
       </c>
       <c r="I5" t="n">
-        <v>3.761535821404534</v>
+        <v>3.945525337149859</v>
       </c>
       <c r="J5" t="n">
-        <v>5.424290154126554</v>
+        <v>5.628877294846307</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6667063428556835</v>
+        <v>0.8332963024058476</v>
       </c>
       <c r="L5" t="n">
-        <v>2.24971873750889</v>
+        <v>2.447016888298298</v>
       </c>
     </row>
     <row r="6">
@@ -78376,32 +78713,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.2349457565428664</v>
+        <v>0.2268902755742741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.777867399028833</v>
+        <v>0.8243025738537696</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.180645399442289</v>
+        <v>-1.12194720071743</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6768454299297242</v>
+        <v>-0.5844061606386622</v>
       </c>
       <c r="I7" t="n">
-        <v>1.244918777026858</v>
+        <v>1.429232587551696</v>
       </c>
       <c r="J7" t="n">
-        <v>1.987428654335395</v>
+        <v>2.193699185623069</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7231563996334756</v>
+        <v>0.8793207684012821</v>
       </c>
       <c r="L7" t="n">
-        <v>1.496177035463338</v>
+        <v>1.689523870967111</v>
       </c>
     </row>
     <row r="8">
@@ -78805,7 +79142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80960,6 +81297,25 @@
       </c>
       <c r="E118" t="n">
         <v>36.53139195359947</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>33.35494295335248</v>
+      </c>
+      <c r="C119" t="n">
+        <v>34.2875054034282</v>
+      </c>
+      <c r="D119" t="n">
+        <v>34.60646688692344</v>
+      </c>
+      <c r="E119" t="n">
+        <v>36.58475252556579</v>
       </c>
     </row>
   </sheetData>
@@ -81044,29 +81400,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12176.766</v>
+        <v>12414.1508</v>
       </c>
       <c r="F2" t="n">
-        <v>12324.50167634108</v>
+        <v>12565.90268236841</v>
       </c>
       <c r="G2" t="n">
-        <v>1.203376168781634</v>
+        <v>1.212642270288233</v>
       </c>
       <c r="H2" t="n">
-        <v>12128.50845815546</v>
+        <v>12355.8215255118</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3930802447854376</v>
+        <v>-0.4661065334788494</v>
       </c>
       <c r="J2" t="n">
-        <v>12643.5949867737</v>
+        <v>12914.82550712655</v>
       </c>
       <c r="K2" t="n">
-        <v>3.802540398454268</v>
+        <v>4.000868417907788</v>
       </c>
     </row>
     <row r="3">
@@ -81167,29 +81523,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>335.9549794131011</v>
+        <v>344.3846493764272</v>
       </c>
       <c r="F5" t="n">
-        <v>349.2735419059107</v>
+        <v>358.0026714776881</v>
       </c>
       <c r="G5" t="n">
-        <v>3.055031625224136</v>
+        <v>3.064467262847659</v>
       </c>
       <c r="H5" t="n">
-        <v>352.4421038497465</v>
+        <v>360.8524510952154</v>
       </c>
       <c r="I5" t="n">
-        <v>3.78184106506616</v>
+        <v>3.705753954799351</v>
       </c>
       <c r="J5" t="n">
-        <v>355.7843083754764</v>
+        <v>365.4850729758622</v>
       </c>
       <c r="K5" t="n">
-        <v>4.548480897974905</v>
+        <v>4.748234132084383</v>
       </c>
     </row>
     <row r="6">
@@ -81249,29 +81605,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59.56269863266965</v>
+        <v>62.64801925394536</v>
       </c>
       <c r="F7" t="n">
-        <v>60.3859546641462</v>
+        <v>63.50216260690051</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5159451667158033</v>
+        <v>0.5251483275806601</v>
       </c>
       <c r="H7" t="n">
-        <v>61.89345232692278</v>
+        <v>64.90285427968483</v>
       </c>
       <c r="I7" t="n">
-        <v>1.460713383657897</v>
+        <v>1.386327995927794</v>
       </c>
       <c r="J7" t="n">
-        <v>62.13453481561319</v>
+        <v>65.58535338689147</v>
       </c>
       <c r="K7" t="n">
-        <v>1.611802886879077</v>
+        <v>1.805945222339278</v>
       </c>
     </row>
     <row r="8">
@@ -81391,25 +81747,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01031201005206184</v>
+        <v>0.01030212536958604</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04516160588280115</v>
+        <v>-0.04469657263504254</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06578562598692482</v>
+        <v>0.06530082337421461</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1238207152522097</v>
+        <v>0.1237019522615235</v>
       </c>
       <c r="I2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J2" t="n">
-        <v>1.203376168781456</v>
+        <v>1.212642270288078</v>
       </c>
     </row>
     <row r="3">
@@ -81427,25 +81783,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01370731035972159</v>
+        <v>0.01429525526100725</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02882326019610368</v>
+        <v>-0.0279267980974306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05623788091554687</v>
+        <v>0.05651730861944511</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1646230795780079</v>
+        <v>0.1716902824140831</v>
       </c>
       <c r="I3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J3" t="n">
-        <v>1.602756532869654</v>
+        <v>1.686610204122707</v>
       </c>
     </row>
     <row r="4">
@@ -81463,25 +81819,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.003395300307659757</v>
+        <v>-0.003993129891421215</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.04475595512745151</v>
+        <v>-0.04499417709118948</v>
       </c>
       <c r="G4" t="n">
-        <v>0.037965354512132</v>
+        <v>0.03700791730834704</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04073530461286001</v>
+        <v>-0.04790608006839392</v>
       </c>
       <c r="I4" t="n">
         <v>58</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.393080244785482</v>
+        <v>-0.4661065334788828</v>
       </c>
     </row>
     <row r="5">
@@ -81499,25 +81855,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0218606265149733</v>
+        <v>0.02322698855401056</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02234571523474711</v>
+        <v>-0.02075206793147282</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06606696826469372</v>
+        <v>0.06720604503949394</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2626718978820497</v>
+        <v>0.2791126587447623</v>
       </c>
       <c r="I5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>2.568258419894942</v>
+        <v>2.754820035399974</v>
       </c>
     </row>
     <row r="6">
@@ -81823,25 +82179,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09119074904323113</v>
+        <v>0.08877794766555944</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.02590230046827823</v>
+        <v>-0.02497891432848736</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2082837985547405</v>
+        <v>0.2025348096596062</v>
       </c>
       <c r="H14" t="n">
-        <v>1.100298229956742</v>
+        <v>1.071030274564722</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>3.055031625224069</v>
+        <v>3.064467262847614</v>
       </c>
     </row>
     <row r="15">
@@ -81859,25 +82215,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02129660813842164</v>
+        <v>-0.01824385896346385</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.112018535363151</v>
+        <v>-0.107165841152617</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06942531908630767</v>
+        <v>0.0706781232256893</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2552330228889788</v>
+        <v>-0.2186868387061724</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.700324288317844</v>
+        <v>-0.6183713704364546</v>
       </c>
     </row>
     <row r="16">
@@ -81895,25 +82251,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1124873571816528</v>
+        <v>0.1070218066290233</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06125232215590267</v>
+        <v>0.05407356892816455</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1637223922074029</v>
+        <v>0.159970044329882</v>
       </c>
       <c r="H16" t="n">
-        <v>1.358999869293176</v>
+        <v>1.292543736306717</v>
       </c>
       <c r="I16" t="n">
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>3.78184106506616</v>
+        <v>3.705753954799373</v>
       </c>
     </row>
     <row r="17">
@@ -81931,25 +82287,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04359928087075662</v>
+        <v>0.04766180158286178</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.04987287688879409</v>
+        <v>-0.0435630099631046</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1370714386303074</v>
+        <v>0.1388866131288282</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5245624065042476</v>
+        <v>0.5735803277348683</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>1.449176473189517</v>
+        <v>1.633702588247554</v>
       </c>
     </row>
     <row r="18">
@@ -82111,25 +82467,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02573093650705654</v>
+        <v>0.02494163011159637</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.05780926400914693</v>
+        <v>-0.0546620489380607</v>
       </c>
       <c r="G22" t="n">
-        <v>0.10927113702326</v>
+        <v>0.1045453091612535</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3092484274868301</v>
+        <v>0.2997479096661815</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5159451667157589</v>
+        <v>0.5251483275806157</v>
       </c>
     </row>
     <row r="23">
@@ -82147,25 +82503,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.04677645002827109</v>
+        <v>-0.04062057794072754</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1148841726415973</v>
+        <v>-0.1082466236921258</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02133127258505513</v>
+        <v>0.02700546781067074</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5597449577266711</v>
+        <v>-0.4862608406916213</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9311665426298132</v>
+        <v>-0.8494041409427111</v>
       </c>
     </row>
     <row r="24">
@@ -82183,25 +82539,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07250738653532762</v>
+        <v>0.06556220805232392</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02465496453858271</v>
+        <v>0.01508453575920563</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1203598085320726</v>
+        <v>0.1160398803454422</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8738849119444447</v>
+        <v>0.7898494790749444</v>
       </c>
       <c r="I24" t="n">
         <v>15</v>
       </c>
       <c r="J24" t="n">
-        <v>1.460713383657897</v>
+        <v>1.386327995927794</v>
       </c>
     </row>
     <row r="25">
@@ -82219,25 +82575,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05421662627048686</v>
+        <v>0.06028845288057473</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.05175234434601708</v>
+        <v>-0.04181933654657934</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1601855968869908</v>
+        <v>0.1623962423077288</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6527205111267698</v>
+        <v>0.7260847391866943</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>1.090232717153206</v>
+        <v>1.274105948677562</v>
       </c>
     </row>
     <row r="26">
@@ -82395,7 +82751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87494,6 +87850,49 @@
       </c>
       <c r="M118" t="n">
         <v>12617.12104892586</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>12523.1733</v>
+      </c>
+      <c r="C119" t="n">
+        <v>12597.42512827453</v>
+      </c>
+      <c r="D119" t="n">
+        <v>12463.7838</v>
+      </c>
+      <c r="E119" t="n">
+        <v>12481.54900372169</v>
+      </c>
+      <c r="F119" t="n">
+        <v>12631.4816</v>
+      </c>
+      <c r="G119" t="n">
+        <v>13064.86520971191</v>
+      </c>
+      <c r="H119" t="n">
+        <v>12615.4271</v>
+      </c>
+      <c r="I119" t="n">
+        <v>13425.18593638132</v>
+      </c>
+      <c r="J119" t="n">
+        <v>12591.9359</v>
+      </c>
+      <c r="K119" t="n">
+        <v>12835.41167554972</v>
+      </c>
+      <c r="L119" t="n">
+        <v>12434.4545</v>
+      </c>
+      <c r="M119" t="n">
+        <v>12812.95984298013</v>
       </c>
     </row>
   </sheetData>
@@ -87578,23 +87977,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12176.812</v>
+        <v>12423.1733</v>
       </c>
       <c r="G2" t="n">
-        <v>12256.21722017382</v>
+        <v>12497.42512827453</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6467902267609738</v>
+        <v>0.5929154416039806</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04655492965786081</v>
+        <v>-0.1147104645052483</v>
       </c>
       <c r="J2" t="n">
-        <v>1.38144804487992</v>
+        <v>1.370476484563019</v>
       </c>
     </row>
     <row r="3">
@@ -87698,23 +88097,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>344.2591195378216</v>
+        <v>353.1741582487014</v>
       </c>
       <c r="G5" t="n">
-        <v>356.4499543630808</v>
+        <v>365.3603948872912</v>
       </c>
       <c r="H5" t="n">
-        <v>2.74408206587673</v>
+        <v>2.689084630439598</v>
       </c>
       <c r="I5" t="n">
-        <v>1.823183083291629</v>
+        <v>1.762951932975506</v>
       </c>
       <c r="J5" t="n">
-        <v>3.711229672000861</v>
+        <v>3.697195701495489</v>
       </c>
     </row>
     <row r="6">
@@ -87778,23 +88177,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59.87982458139483</v>
+        <v>63.08816575560557</v>
       </c>
       <c r="G7" t="n">
-        <v>60.027846337136</v>
+        <v>63.15177831122112</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09258313619542324</v>
+        <v>0.03900501015559055</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3581835249323923</v>
+        <v>-0.4600804129458854</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5479805963517418</v>
+        <v>0.5178612350010995</v>
       </c>
     </row>
     <row r="8">
@@ -87858,23 +88257,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12123.9951</v>
+        <v>12363.7838</v>
       </c>
       <c r="G9" t="n">
-        <v>12136.60889340963</v>
+        <v>12381.54900372169</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1031887963504508</v>
+        <v>0.1425345946845402</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6236327540364972</v>
+        <v>-0.6001674115214726</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8082068957967744</v>
+        <v>0.8612472612780046</v>
       </c>
     </row>
     <row r="10">
@@ -87978,23 +88377,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>328.6189935374019</v>
+        <v>337.0268823180218</v>
       </c>
       <c r="G12" t="n">
-        <v>337.0349909309125</v>
+        <v>345.7831171333034</v>
       </c>
       <c r="H12" t="n">
-        <v>1.963514804617761</v>
+        <v>2.003591808549166</v>
       </c>
       <c r="I12" t="n">
-        <v>1.11929262698889</v>
+        <v>1.114484503427043</v>
       </c>
       <c r="J12" t="n">
-        <v>2.849347992807571</v>
+        <v>2.924040988945939</v>
       </c>
     </row>
     <row r="13">
@@ -88058,23 +88457,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>59.01595181440085</v>
+        <v>62.13524530665999</v>
       </c>
       <c r="G14" t="n">
-        <v>59.15740119450934</v>
+        <v>62.34325372482592</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08895294999937686</v>
+        <v>0.1282931528999276</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.417156030017037</v>
+        <v>-0.4275705905422519</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5950525681667891</v>
+        <v>0.6567537019317672</v>
       </c>
     </row>
     <row r="15">
@@ -88138,23 +88537,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12297.9365</v>
+        <v>12531.4816</v>
       </c>
       <c r="G16" t="n">
-        <v>12721.95932626097</v>
+        <v>12964.86520971191</v>
       </c>
       <c r="H16" t="n">
-        <v>3.420108066055794</v>
+        <v>3.430980018305285</v>
       </c>
       <c r="I16" t="n">
-        <v>2.601363854781046</v>
+        <v>2.612199313979563</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1849306556201</v>
+        <v>4.207513707459279</v>
       </c>
     </row>
     <row r="17">
@@ -88258,23 +88657,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>328.1473811149363</v>
+        <v>336.2125718777076</v>
       </c>
       <c r="G19" t="n">
-        <v>352.6996193876979</v>
+        <v>361.2757970363082</v>
       </c>
       <c r="H19" t="n">
-        <v>5.734529593250159</v>
+        <v>5.745644847124476</v>
       </c>
       <c r="I19" t="n">
-        <v>4.41436095854769</v>
+        <v>4.38609073293946</v>
       </c>
       <c r="J19" t="n">
-        <v>7.123992467793827</v>
+        <v>7.169855687835818</v>
       </c>
     </row>
     <row r="20">
@@ -88338,23 +88737,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>60.73784337664774</v>
+        <v>63.76572916273668</v>
       </c>
       <c r="G21" t="n">
-        <v>63.63353176881996</v>
+        <v>66.73349072088854</v>
       </c>
       <c r="H21" t="n">
-        <v>1.80149760090218</v>
+        <v>1.812199398082082</v>
       </c>
       <c r="I21" t="n">
-        <v>1.120565275407799</v>
+        <v>1.095324160777219</v>
       </c>
       <c r="J21" t="n">
-        <v>2.51481784334033</v>
+        <v>2.577096625518531</v>
       </c>
     </row>
     <row r="22">
@@ -88418,23 +88817,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12304.6845</v>
+        <v>12515.4271</v>
       </c>
       <c r="G23" t="n">
-        <v>13057.41757618012</v>
+        <v>13325.18593638132</v>
       </c>
       <c r="H23" t="n">
-        <v>6.068135599741531</v>
+        <v>6.418798428008166</v>
       </c>
       <c r="I23" t="n">
-        <v>5.039725658920387</v>
+        <v>5.377499788456092</v>
       </c>
       <c r="J23" t="n">
-        <v>7.050042305716657</v>
+        <v>7.400659380517513</v>
       </c>
     </row>
     <row r="24">
@@ -88538,23 +88937,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>319.4944059226474</v>
+        <v>326.6211766026752</v>
       </c>
       <c r="G26" t="n">
-        <v>357.0958949412391</v>
+        <v>366.3983144726141</v>
       </c>
       <c r="H26" t="n">
-        <v>8.963525731860456</v>
+        <v>9.323760762814759</v>
       </c>
       <c r="I26" t="n">
-        <v>7.119757686665275</v>
+        <v>7.47148872043567</v>
       </c>
       <c r="J26" t="n">
-        <v>11.00356306829025</v>
+        <v>11.38517666187032</v>
       </c>
     </row>
     <row r="27">
@@ -88618,23 +89017,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>60.32410073081473</v>
+        <v>63.04783931769084</v>
       </c>
       <c r="G28" t="n">
-        <v>66.13394821179936</v>
+        <v>69.51496235297547</v>
       </c>
       <c r="H28" t="n">
-        <v>3.623814170484208</v>
+        <v>3.966396035879849</v>
       </c>
       <c r="I28" t="n">
-        <v>2.596106636411232</v>
+        <v>2.913686603359522</v>
       </c>
       <c r="J28" t="n">
-        <v>4.742763000988196</v>
+        <v>5.123588905150087</v>
       </c>
     </row>
     <row r="29">
@@ -88698,23 +89097,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>12260.9149</v>
+        <v>12491.9359</v>
       </c>
       <c r="G30" t="n">
-        <v>12494.47866753195</v>
+        <v>12735.41167554972</v>
       </c>
       <c r="H30" t="n">
-        <v>1.889534629284984</v>
+        <v>1.933584934701882</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8492079816932414</v>
+        <v>0.89188187605562</v>
       </c>
       <c r="J30" t="n">
-        <v>2.85601979624055</v>
+        <v>2.902326371761335</v>
       </c>
     </row>
     <row r="31">
@@ -88818,23 +89217,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>332.1387782984502</v>
+        <v>340.2152947625581</v>
       </c>
       <c r="G33" t="n">
-        <v>345.9287056454017</v>
+        <v>354.4593441298346</v>
       </c>
       <c r="H33" t="n">
-        <v>3.191087687443717</v>
+        <v>3.23570069844108</v>
       </c>
       <c r="I33" t="n">
-        <v>1.888122951646849</v>
+        <v>1.914587202024166</v>
       </c>
       <c r="J33" t="n">
-        <v>4.715648962188207</v>
+        <v>4.769893865160716</v>
       </c>
     </row>
     <row r="34">
@@ -88898,23 +89297,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>58.70375463236866</v>
+        <v>61.66987003689461</v>
       </c>
       <c r="G35" t="n">
-        <v>60.18567307900682</v>
+        <v>63.25003303189396</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9337639491081795</v>
+        <v>0.977401042407422</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3263605659709072</v>
+        <v>0.3513086593990892</v>
       </c>
       <c r="J35" t="n">
-        <v>1.655113077848652</v>
+        <v>1.715717921758231</v>
       </c>
     </row>
     <row r="36">
@@ -88978,23 +89377,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>12165.2749</v>
+        <v>12334.4545</v>
       </c>
       <c r="G37" t="n">
-        <v>12517.12104892586</v>
+        <v>12712.95984298013</v>
       </c>
       <c r="H37" t="n">
-        <v>2.86863646998945</v>
+        <v>3.044004407110346</v>
       </c>
       <c r="I37" t="n">
-        <v>1.846663974948485</v>
+        <v>2.038846890432266</v>
       </c>
       <c r="J37" t="n">
-        <v>3.858755768455382</v>
+        <v>4.039828003970996</v>
       </c>
     </row>
     <row r="38">
@@ -89098,23 +89497,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>344.0227121667822</v>
+        <v>350.1472862548275</v>
       </c>
       <c r="G40" t="n">
-        <v>367.6546202967877</v>
+        <v>374.9134011642841</v>
       </c>
       <c r="H40" t="n">
-        <v>5.322229580258253</v>
+        <v>5.501780342942353</v>
       </c>
       <c r="I40" t="n">
-        <v>3.671233120986118</v>
+        <v>3.81856952725536</v>
       </c>
       <c r="J40" t="n">
-        <v>7.062488383780186</v>
+        <v>7.268293020342762</v>
       </c>
     </row>
     <row r="41">
@@ -89178,23 +89577,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>58.93656907890645</v>
+        <v>61.1288416045016</v>
       </c>
       <c r="G42" t="n">
-        <v>60.53438732341129</v>
+        <v>63.02614916795144</v>
       </c>
       <c r="H42" t="n">
-        <v>1.005318193141314</v>
+        <v>1.17750959080738</v>
       </c>
       <c r="I42" t="n">
-        <v>0.273142069623669</v>
+        <v>0.425408027063364</v>
       </c>
       <c r="J42" t="n">
-        <v>1.75924866766265</v>
+        <v>1.955509433978903</v>
       </c>
     </row>
     <row r="43">
